--- a/data processing/goFlux_reprocessing/results/CO2_best_all.xlsx
+++ b/data processing/goFlux_reprocessing/results/CO2_best_all.xlsx
@@ -146,130 +146,130 @@
     <t xml:space="preserve">2 0.5 stem 1</t>
   </si>
   <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Noise (LM.MAE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 1.25 stem 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">Noise (HM.MAE)</t>
   </si>
   <si>
-    <t xml:space="preserve">Noise (LM.MAE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HM</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">2 1.25 stem 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 1.7 stem 1</t>
   </si>
   <si>
     <t xml:space="preserve">2 10.5 leaf 1</t>
   </si>
   <si>
+    <t xml:space="preserve">AICc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 leaf 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 stem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 leaf 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 leaf 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 leaf_s 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 stem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 7 leaf 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 9.1 branch 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 9.1 leaf 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 12 leaf 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 14.2 leaf 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 3 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 5.6 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 5.6 stem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 9.1 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 9.1 stem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 0.5 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 1 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 1 stem 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 2 stem 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 branch 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exaggerated curvature (g-fact)</t>
+  </si>
+  <si>
     <t xml:space="preserve">LM</t>
   </si>
   <si>
+    <t xml:space="preserve">g-fact. &gt; 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 branch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 branch 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noise (HM.MAE) | Exaggerated curvature (g-fact)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 10.5 branch 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 branch 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 11.7 branch 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 3 stem 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">MAE | AICc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 leaf 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 stem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 leaf 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 leaf 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 leaf_s 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AICc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 stem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 7 leaf 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 9.1 branch 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 9.1 leaf 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 12 leaf 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 14.2 leaf 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 3 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 5.6 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 5.6 stem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 9.1 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 9.1 stem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 0.5 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 1 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 1 stem 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 2 stem 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 branch 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noise (HM.MAE) | Exaggerated curvature (g-fact)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g-fact. &gt; 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 branch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 branch 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 10.5 branch 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exaggerated curvature (g-fact)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 branch 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 11.7 branch 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 3 stem 1</t>
   </si>
   <si>
     <t xml:space="preserve">2 3 stem 2</t>
@@ -1124,10 +1124,10 @@
         <v>650.923</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.00351834090683244</v>
+        <v>0.0248163791207175</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB2" t="n">
         <v>1.56817480418817</v>
@@ -1136,7 +1136,7 @@
         <v>157</v>
       </c>
       <c r="AD2" t="n">
-        <v>3.68317892936242</v>
+        <v>0.522182508226625</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -1157,7 +1157,7 @@
         <v>46</v>
       </c>
       <c r="AK2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -1166,7 +1166,7 @@
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO2" t="n">
         <v>2</v>
@@ -1175,12 +1175,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.0035</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" t="n">
         <v>2.45018888762851</v>
@@ -1255,10 +1255,10 @@
         <v>631.441</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.00412843782156025</v>
+        <v>0.0291196563576855</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB3" t="n">
         <v>1.5688063721929</v>
@@ -1267,7 +1267,7 @@
         <v>134</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.46233506124351</v>
+        <v>0.632647329797554</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1276,7 +1276,7 @@
         <v>1.47662162526974</v>
       </c>
       <c r="AG3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH3" t="s">
         <v>45</v>
@@ -1288,7 +1288,7 @@
         <v>46</v>
       </c>
       <c r="AK3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO3" t="n">
         <v>2</v>
@@ -1306,7 +1306,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0041</v>
+        <v>0.029</v>
       </c>
     </row>
     <row r="4">
@@ -1386,10 +1386,10 @@
         <v>786.042</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.00460298833110823</v>
+        <v>0.0324668662127631</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB4" t="n">
         <v>1.5650160325768</v>
@@ -1398,7 +1398,7 @@
         <v>120</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.11676003019415</v>
+        <v>0.583653447079755</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1410,7 +1410,7 @@
         <v>44</v>
       </c>
       <c r="AH4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI4" t="n">
         <v>2.67238050035663</v>
@@ -1419,7 +1419,7 @@
         <v>46</v>
       </c>
       <c r="AK4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1428,7 +1428,7 @@
         <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO4" t="n">
         <v>2</v>
@@ -1437,7 +1437,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.0046</v>
+        <v>0.032</v>
       </c>
     </row>
     <row r="5">
@@ -1517,10 +1517,10 @@
         <v>277.555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00105839509970564</v>
+        <v>0.00746531810001655</v>
       </c>
       <c r="AA5" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB5" t="n">
         <v>0.749948527791428</v>
@@ -1529,7 +1529,7 @@
         <v>250</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.00398243584854</v>
+        <v>0.142339559554773</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1541,25 +1541,25 @@
         <v>44</v>
       </c>
       <c r="AH5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.263527302392572</v>
+        <v>-0.300098826663761</v>
       </c>
       <c r="AJ5" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK5" t="s">
         <v>51</v>
       </c>
-      <c r="AK5" t="s">
-        <v>52</v>
-      </c>
       <c r="AL5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO5" t="n">
         <v>2</v>
@@ -1568,12 +1568,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0011</v>
+        <v>0.0075</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="n">
         <v>-0.658380583624297</v>
@@ -1648,10 +1648,10 @@
         <v>293.745</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.00146247668156579</v>
+        <v>0.0103154801498813</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB6" t="n">
         <v>0.747952360000791</v>
@@ -1660,7 +1660,7 @@
         <v>180</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.514982881773</v>
+        <v>0.35656157209245</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1672,25 +1672,25 @@
         <v>44</v>
       </c>
       <c r="AH6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.658380583624297</v>
+        <v>-0.806475562382559</v>
       </c>
       <c r="AJ6" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK6" t="s">
         <v>51</v>
       </c>
-      <c r="AK6" t="s">
-        <v>52</v>
-      </c>
       <c r="AL6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO6" t="n">
         <v>2</v>
@@ -1699,12 +1699,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="n">
         <v>1.35575329922547</v>
@@ -1779,10 +1779,10 @@
         <v>859.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.00132995747504917</v>
+        <v>0.00938076490858482</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB7" t="n">
         <v>1.54275067105703</v>
@@ -1791,7 +1791,7 @@
         <v>408</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.51082752877748</v>
+        <v>0.355972447129644</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1812,7 +1812,7 @@
         <v>46</v>
       </c>
       <c r="AK7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO7" t="n">
         <v>2</v>
@@ -1830,12 +1830,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.0013</v>
+        <v>0.0094</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B8" t="n">
         <v>2.71060561835878</v>
@@ -1910,10 +1910,10 @@
         <v>1086.74</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.00148812773525868</v>
+        <v>0.0104964081185305</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB8" t="n">
         <v>1.54340105113971</v>
@@ -1922,7 +1922,7 @@
         <v>365</v>
       </c>
       <c r="AD8" t="n">
-        <v>5.01787106812332</v>
+        <v>0.711408419347151</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1943,7 +1943,7 @@
         <v>46</v>
       </c>
       <c r="AK8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1952,7 +1952,7 @@
         <v>2</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1961,12 +1961,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.0015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B9" t="n">
         <v>-0.490131414829546</v>
@@ -2041,10 +2041,10 @@
         <v>254.221</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00122507361132055</v>
+        <v>0.00864097368457913</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB9" t="n">
         <v>0.749045008064568</v>
@@ -2053,7 +2053,7 @@
         <v>215</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.86954783205878</v>
+        <v>0.265055050247883</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2074,7 +2074,7 @@
         <v>46</v>
       </c>
       <c r="AK9" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO9" t="n">
         <v>2</v>
@@ -2092,12 +2092,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0012</v>
+        <v>0.0086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B10" t="n">
         <v>-0.395758448378302</v>
@@ -2172,10 +2172,10 @@
         <v>277.161</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.00126845238657178</v>
+        <v>0.008946942935693</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB10" t="n">
         <v>0.75019898291531</v>
@@ -2184,7 +2184,7 @@
         <v>209</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.5072513422291</v>
+        <v>0.213690483549053</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2196,25 +2196,25 @@
         <v>44</v>
       </c>
       <c r="AH10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.395758448378302</v>
+        <v>-0.461160692941333</v>
       </c>
       <c r="AJ10" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK10" t="s">
         <v>51</v>
       </c>
-      <c r="AK10" t="s">
-        <v>52</v>
-      </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2223,12 +2223,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0013</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B11" t="n">
         <v>0.340678943816397</v>
@@ -2303,10 +2303,10 @@
         <v>335.969</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0014586511644609</v>
+        <v>0.0102884971242673</v>
       </c>
       <c r="AA11" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB11" t="n">
         <v>0.74599588125286</v>
@@ -2315,7 +2315,7 @@
         <v>180</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3047905965235</v>
+        <v>0.184986621467532</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2327,7 +2327,7 @@
         <v>44</v>
       </c>
       <c r="AH11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI11" t="n">
         <v>0.346085541661996</v>
@@ -2336,7 +2336,7 @@
         <v>46</v>
       </c>
       <c r="AK11" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AL11" t="n">
         <v>1</v>
@@ -2345,7 +2345,7 @@
         <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO11" t="n">
         <v>2</v>
@@ -2354,12 +2354,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12" t="n">
         <v>2.75354993265132</v>
@@ -2434,10 +2434,10 @@
         <v>1687.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.00146325201209299</v>
+        <v>0.0103209488912046</v>
       </c>
       <c r="AA12" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB12" t="n">
         <v>1.53432425268036</v>
@@ -2446,7 +2446,7 @@
         <v>369</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.12752471201397</v>
+        <v>0.726954559217396</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2455,7 +2455,7 @@
         <v>1.56730904485439</v>
       </c>
       <c r="AG12" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH12" t="s">
         <v>45</v>
@@ -2467,7 +2467,7 @@
         <v>46</v>
       </c>
       <c r="AK12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2476,7 +2476,7 @@
         <v>2</v>
       </c>
       <c r="AN12" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2485,12 +2485,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.0015</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B13" t="n">
         <v>2.38225332097811</v>
@@ -2565,10 +2565,10 @@
         <v>1133.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.00140830602350497</v>
+        <v>0.00993339108482071</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB13" t="n">
         <v>1.53706543136828</v>
@@ -2577,7 +2577,7 @@
         <v>384</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.4282031987919</v>
+        <v>0.627808286708079</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2598,7 +2598,7 @@
         <v>46</v>
       </c>
       <c r="AK13" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>2</v>
       </c>
       <c r="AN13" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO13" t="n">
         <v>2</v>
@@ -2616,12 +2616,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.0014</v>
+        <v>0.0099</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B14" t="n">
         <v>-0.236992797939244</v>
@@ -2696,10 +2696,10 @@
         <v>339.96</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.00130237897214424</v>
+        <v>0.00918624180755692</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB14" t="n">
         <v>0.747937638288551</v>
@@ -2708,7 +2708,7 @@
         <v>202</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.90531916721803</v>
+        <v>0.128351579586546</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2720,25 +2720,25 @@
         <v>44</v>
       </c>
       <c r="AH14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.236992797939244</v>
+        <v>-0.257758382004878</v>
       </c>
       <c r="AJ14" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK14" t="s">
         <v>51</v>
       </c>
-      <c r="AK14" t="s">
-        <v>52</v>
-      </c>
       <c r="AL14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN14" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2747,12 +2747,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0013</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B15" t="n">
         <v>0.66988247761425</v>
@@ -2827,10 +2827,10 @@
         <v>572.069</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.00179945757832536</v>
+        <v>0.0126923520653302</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB15" t="n">
         <v>1.84572934462516</v>
@@ -2839,7 +2839,7 @@
         <v>360</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.03696131917403</v>
+        <v>0.147015139086391</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -2860,7 +2860,7 @@
         <v>46</v>
       </c>
       <c r="AK15" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2869,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO15" t="n">
         <v>2</v>
@@ -2878,12 +2878,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.0018</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B16" t="n">
         <v>-0.313144471260615</v>
@@ -2958,10 +2958,10 @@
         <v>263.572</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.000953532614246482</v>
+        <v>0.00672567766618544</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AB16" t="n">
         <v>0.746479818010103</v>
@@ -2970,7 +2970,7 @@
         <v>275</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19855683667517</v>
+        <v>0.16992533548609</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -2982,25 +2982,25 @@
         <v>44</v>
       </c>
       <c r="AH16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.313144471260615</v>
+        <v>-0.371713531323036</v>
       </c>
       <c r="AJ16" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK16" t="s">
         <v>51</v>
       </c>
-      <c r="AK16" t="s">
-        <v>52</v>
-      </c>
       <c r="AL16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.35</v>
+        <v>2.46870127774823</v>
       </c>
       <c r="AO16" t="n">
         <v>2</v>
@@ -3009,12 +3009,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.00095</v>
+        <v>0.0067</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B17" t="n">
         <v>-0.67204166927984</v>
@@ -3089,10 +3089,10 @@
         <v>332.541</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.00299948189885121</v>
+        <v>0.0249284415466051</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB17" t="n">
         <v>1.68827981163911</v>
@@ -3101,7 +3101,7 @@
         <v>198</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.13732276003529</v>
+        <v>0.136846863270598</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3113,25 +3113,25 @@
         <v>44</v>
       </c>
       <c r="AH17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.67204166927984</v>
+        <v>-0.7436045017802</v>
       </c>
       <c r="AJ17" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK17" t="s">
         <v>51</v>
       </c>
-      <c r="AK17" t="s">
-        <v>52</v>
-      </c>
       <c r="AL17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO17" t="n">
         <v>2</v>
@@ -3140,12 +3140,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B18" t="n">
         <v>-1.29649991085757</v>
@@ -3220,10 +3220,10 @@
         <v>205.108</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.00186933627823421</v>
+        <v>0.0155358964362336</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB18" t="n">
         <v>1.6930845720007</v>
@@ -3232,7 +3232,7 @@
         <v>318</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.18789156835547</v>
+        <v>0.263255171554242</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3253,7 +3253,7 @@
         <v>46</v>
       </c>
       <c r="AK18" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
@@ -3262,7 +3262,7 @@
         <v>2</v>
       </c>
       <c r="AN18" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO18" t="n">
         <v>2</v>
@@ -3271,12 +3271,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.0019</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B19" t="n">
         <v>0.299385274549928</v>
@@ -3351,10 +3351,10 @@
         <v>799.081</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.00395209209390884</v>
+        <v>0.0328455046811715</v>
       </c>
       <c r="AA19" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB19" t="n">
         <v>2.12283803901389</v>
@@ -3363,7 +3363,7 @@
         <v>189</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.402944776282334</v>
+        <v>0.0484837995362012</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3375,7 +3375,7 @@
         <v>44</v>
       </c>
       <c r="AH19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI19" t="n">
         <v>0.491427468196859</v>
@@ -3384,7 +3384,7 @@
         <v>46</v>
       </c>
       <c r="AK19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -3393,7 +3393,7 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
@@ -3402,12 +3402,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.004</v>
+        <v>0.033</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B20" t="n">
         <v>1.16978053059415</v>
@@ -3482,10 +3482,10 @@
         <v>776.278</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.00149698330590518</v>
+        <v>0.0124413022301596</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB20" t="n">
         <v>1.56541682846084</v>
@@ -3494,7 +3494,7 @@
         <v>368</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.13504162383255</v>
+        <v>0.25689607158181</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -3515,7 +3515,7 @@
         <v>46</v>
       </c>
       <c r="AK20" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
@@ -3524,7 +3524,7 @@
         <v>2</v>
       </c>
       <c r="AN20" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO20" t="n">
         <v>2</v>
@@ -3533,12 +3533,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0.0015</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B21" t="n">
         <v>1.90883677402145</v>
@@ -3613,10 +3613,10 @@
         <v>832.232</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.00304397096109333</v>
+        <v>0.0252981863975377</v>
       </c>
       <c r="AA21" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB21" t="n">
         <v>2.12208261287649</v>
@@ -3625,7 +3625,7 @@
         <v>245</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.57003159125569</v>
+        <v>0.309235666539172</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -3637,7 +3637,7 @@
         <v>44</v>
       </c>
       <c r="AH21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI21" t="n">
         <v>1.94249220540607</v>
@@ -3646,7 +3646,7 @@
         <v>46</v>
       </c>
       <c r="AK21" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -3655,7 +3655,7 @@
         <v>2</v>
       </c>
       <c r="AN21" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO21" t="n">
         <v>2</v>
@@ -3664,12 +3664,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.003</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B22" t="n">
         <v>1.26683236944453</v>
@@ -3744,10 +3744,10 @@
         <v>840.449</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.0016814827645206</v>
+        <v>0.0139746616984186</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB22" t="n">
         <v>1.56137685276913</v>
@@ -3756,7 +3756,7 @@
         <v>326</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.31815980180346</v>
+        <v>0.278929525183291</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -3777,7 +3777,7 @@
         <v>46</v>
       </c>
       <c r="AK22" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
@@ -3786,7 +3786,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO22" t="n">
         <v>2</v>
@@ -3795,12 +3795,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.0017</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B23" t="n">
         <v>1.31136945330689</v>
@@ -3875,10 +3875,10 @@
         <v>692.178</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.00232801750507625</v>
+        <v>0.0193479574979244</v>
       </c>
       <c r="AA23" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB23" t="n">
         <v>1.56309746769405</v>
@@ -3887,7 +3887,7 @@
         <v>236</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.39701614520464</v>
+        <v>0.288417810850858</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -3908,7 +3908,7 @@
         <v>46</v>
       </c>
       <c r="AK23" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -3917,7 +3917,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO23" t="n">
         <v>2</v>
@@ -3926,12 +3926,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0.0023</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B24" t="n">
         <v>2.43169492750268</v>
@@ -4006,10 +4006,10 @@
         <v>989.409</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.00225843670677889</v>
+        <v>0.0187696773410126</v>
       </c>
       <c r="AA24" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB24" t="n">
         <v>2.10357247545691</v>
@@ -4018,7 +4018,7 @@
         <v>328</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.3028098028121</v>
+        <v>0.397406239790886</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -4039,7 +4039,7 @@
         <v>46</v>
       </c>
       <c r="AK24" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -4048,7 +4048,7 @@
         <v>2</v>
       </c>
       <c r="AN24" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO24" t="n">
         <v>2</v>
@@ -4057,12 +4057,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.0023</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B25" t="n">
         <v>6.03093215874689</v>
@@ -4137,10 +4137,10 @@
         <v>1584.01</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.00322519983053862</v>
+        <v>0.026804364274542</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB25" t="n">
         <v>2.10098731817944</v>
@@ -4149,7 +4149,7 @@
         <v>229</v>
       </c>
       <c r="AD25" t="n">
-        <v>8.20149393105719</v>
+        <v>0.98683395605588</v>
       </c>
       <c r="AE25" t="n">
         <v>1</v>
@@ -4158,7 +4158,7 @@
         <v>1.02946221879342</v>
       </c>
       <c r="AG25" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH25" t="s">
         <v>45</v>
@@ -4170,7 +4170,7 @@
         <v>46</v>
       </c>
       <c r="AK25" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4179,7 +4179,7 @@
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO25" t="n">
         <v>2</v>
@@ -4188,12 +4188,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.0032</v>
+        <v>0.027</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B26" t="n">
         <v>2.51305263324047</v>
@@ -4268,10 +4268,10 @@
         <v>1082.06</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.00262888707722789</v>
+        <v>0.0218484591830343</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB26" t="n">
         <v>2.10310966178231</v>
@@ -4280,7 +4280,7 @@
         <v>281</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.41406371296974</v>
+        <v>0.410792720011496</v>
       </c>
       <c r="AE26" t="n">
         <v>1</v>
@@ -4289,7 +4289,7 @@
         <v>1.06181837185977</v>
       </c>
       <c r="AG26" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH26" t="s">
         <v>45</v>
@@ -4301,7 +4301,7 @@
         <v>46</v>
       </c>
       <c r="AK26" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -4310,7 +4310,7 @@
         <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -4319,12 +4319,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.0026</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B27" t="n">
         <v>5.47320250727151</v>
@@ -4399,10 +4399,10 @@
         <v>1585.98</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.0025920484068107</v>
+        <v>0.0215422960945018</v>
       </c>
       <c r="AA27" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AB27" t="n">
         <v>2.10326213581211</v>
@@ -4411,7 +4411,7 @@
         <v>286</v>
       </c>
       <c r="AD27" t="n">
-        <v>7.43498453335165</v>
+        <v>0.89460472225405</v>
       </c>
       <c r="AE27" t="n">
         <v>1</v>
@@ -4423,7 +4423,7 @@
         <v>44</v>
       </c>
       <c r="AH27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI27" t="n">
         <v>5.78036815961039</v>
@@ -4432,7 +4432,7 @@
         <v>46</v>
       </c>
       <c r="AK27" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL27" t="n">
         <v>0</v>
@@ -4441,7 +4441,7 @@
         <v>2</v>
       </c>
       <c r="AN27" t="n">
-        <v>0.35</v>
+        <v>2.90882053485751</v>
       </c>
       <c r="AO27" t="n">
         <v>2</v>
@@ -4450,12 +4450,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.0026</v>
+        <v>0.022</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B28" t="n">
         <v>0.549430877813202</v>
@@ -4530,10 +4530,10 @@
         <v>677.46</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.00129842711674203</v>
+        <v>0.00253965806825292</v>
       </c>
       <c r="AA28" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB28" t="n">
         <v>1.84747629753581</v>
@@ -4542,7 +4542,7 @@
         <v>51</v>
       </c>
       <c r="AD28" t="n">
-        <v>0.849701027359078</v>
+        <v>0.426707086222678</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -4551,7 +4551,7 @@
         <v>2.75227217493922</v>
       </c>
       <c r="AG28" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AH28" t="s">
         <v>45</v>
@@ -4560,10 +4560,10 @@
         <v>0.549430877813202</v>
       </c>
       <c r="AJ28" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>2</v>
       </c>
       <c r="AN28" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO28" t="n">
         <v>2</v>
@@ -4581,12 +4581,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0.0013</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B29" t="n">
         <v>0.0867317098963377</v>
@@ -4661,10 +4661,10 @@
         <v>515.843</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.00358414221351673</v>
+        <v>0.0067972340240754</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB29" t="n">
         <v>1.84327313838003</v>
@@ -4673,7 +4673,7 @@
         <v>19</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.134437420183908</v>
+        <v>0.0675124520259373</v>
       </c>
       <c r="AE29" t="n">
         <v>1</v>
@@ -4682,7 +4682,7 @@
         <v>6.76116615546377</v>
       </c>
       <c r="AG29" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AH29" t="s">
         <v>45</v>
@@ -4691,10 +4691,10 @@
         <v>0.0867317098963377</v>
       </c>
       <c r="AJ29" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="n">
         <v>0</v>
@@ -4703,7 +4703,7 @@
         <v>2</v>
       </c>
       <c r="AN29" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO29" t="n">
         <v>2</v>
@@ -4712,12 +4712,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.0036</v>
+        <v>0.0068</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B30" t="n">
         <v>0.739644636289007</v>
@@ -4792,10 +4792,10 @@
         <v>612.879</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.00170275630064968</v>
+        <v>0.00331204530299695</v>
       </c>
       <c r="AA30" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB30" t="n">
         <v>1.84384182270351</v>
@@ -4804,7 +4804,7 @@
         <v>39</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.14612347077506</v>
+        <v>0.575565982526671</v>
       </c>
       <c r="AE30" t="n">
         <v>1</v>
@@ -4813,7 +4813,7 @@
         <v>2.40705099280451</v>
       </c>
       <c r="AG30" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH30" t="s">
         <v>45</v>
@@ -4822,10 +4822,10 @@
         <v>0.739644636289007</v>
       </c>
       <c r="AJ30" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -4834,7 +4834,7 @@
         <v>2</v>
       </c>
       <c r="AN30" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO30" t="n">
         <v>2</v>
@@ -4843,7 +4843,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.0017</v>
+        <v>0.0033</v>
       </c>
     </row>
     <row r="31">
@@ -4923,10 +4923,10 @@
         <v>489.658</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.00321384229257319</v>
+        <v>0.00612413223086576</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB31" t="n">
         <v>1.83648131004182</v>
@@ -4935,7 +4935,7 @@
         <v>21</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.946064836099562</v>
+        <v>0.475099542770332</v>
       </c>
       <c r="AE31" t="n">
         <v>1</v>
@@ -4944,7 +4944,7 @@
         <v>2.23861802835215</v>
       </c>
       <c r="AG31" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH31" t="s">
         <v>45</v>
@@ -4953,10 +4953,10 @@
         <v>0.608100636354619</v>
       </c>
       <c r="AJ31" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
@@ -4965,7 +4965,7 @@
         <v>2</v>
       </c>
       <c r="AN31" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO31" t="n">
         <v>2</v>
@@ -4974,12 +4974,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.0032</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B32" t="n">
         <v>3.6639815439635</v>
@@ -5054,10 +5054,10 @@
         <v>1291.85</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.00179253479136743</v>
+        <v>0.00348217434701428</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB32" t="n">
         <v>1.83862854314545</v>
@@ -5066,7 +5066,7 @@
         <v>37</v>
       </c>
       <c r="AD32" t="n">
-        <v>5.69365614172912</v>
+        <v>2.85926854736447</v>
       </c>
       <c r="AE32" t="n">
         <v>1</v>
@@ -5075,7 +5075,7 @@
         <v>1.85518488535681</v>
       </c>
       <c r="AG32" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH32" t="s">
         <v>45</v>
@@ -5087,7 +5087,7 @@
         <v>46</v>
       </c>
       <c r="AK32" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2</v>
       </c>
       <c r="AN32" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO32" t="n">
         <v>2</v>
@@ -5105,12 +5105,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.0018</v>
+        <v>0.0035</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B33" t="n">
         <v>1.84977979296262</v>
@@ -5185,10 +5185,10 @@
         <v>846.208</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.00174455965763363</v>
+        <v>0.00339122558323879</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB33" t="n">
         <v>1.83926432476231</v>
@@ -5197,7 +5197,7 @@
         <v>38</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.87347775498953</v>
+        <v>1.44301734454548</v>
       </c>
       <c r="AE33" t="n">
         <v>1</v>
@@ -5206,7 +5206,7 @@
         <v>2.3868712265464</v>
       </c>
       <c r="AG33" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH33" t="s">
         <v>45</v>
@@ -5215,10 +5215,10 @@
         <v>1.84977979296262</v>
       </c>
       <c r="AJ33" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
@@ -5227,7 +5227,7 @@
         <v>2</v>
       </c>
       <c r="AN33" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO33" t="n">
         <v>2</v>
@@ -5236,12 +5236,12 @@
         <v>0.5</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.0017</v>
+        <v>0.0034</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B34" t="n">
         <v>2.01984230890534</v>
@@ -5316,10 +5316,10 @@
         <v>588.56</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.00411260525037707</v>
+        <v>0.00765917276569363</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB34" t="n">
         <v>1.5275390929972</v>
@@ -5328,7 +5328,7 @@
         <v>14</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.77795766530633</v>
+        <v>1.89723356254604</v>
       </c>
       <c r="AE34" t="n">
         <v>1</v>
@@ -5337,7 +5337,7 @@
         <v>1.01434109020007</v>
       </c>
       <c r="AG34" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH34" t="s">
         <v>45</v>
@@ -5346,10 +5346,10 @@
         <v>2.01984230890534</v>
       </c>
       <c r="AJ34" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK34" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL34" t="n">
         <v>2</v>
@@ -5358,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO34" t="n">
         <v>2</v>
@@ -5367,7 +5367,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.0041</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="35">
@@ -5447,10 +5447,10 @@
         <v>621.681</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.00314495450488175</v>
+        <v>0.00594766564140762</v>
       </c>
       <c r="AA35" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB35" t="n">
         <v>1.52754933094256</v>
@@ -5459,7 +5459,7 @@
         <v>18</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.88193755587138</v>
+        <v>1.44726572941038</v>
       </c>
       <c r="AE35" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
         <v>1.64739085510707</v>
       </c>
       <c r="AG35" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH35" t="s">
         <v>45</v>
@@ -5480,7 +5480,7 @@
         <v>46</v>
       </c>
       <c r="AK35" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL35" t="n">
         <v>0</v>
@@ -5489,7 +5489,7 @@
         <v>2</v>
       </c>
       <c r="AN35" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO35" t="n">
         <v>2</v>
@@ -5498,7 +5498,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.0031</v>
+        <v>0.0059</v>
       </c>
     </row>
     <row r="36">
@@ -5578,10 +5578,10 @@
         <v>750.715</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.0044446547436413</v>
+        <v>0.00823314672227439</v>
       </c>
       <c r="AA36" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB36" t="n">
         <v>1.5238816263913</v>
@@ -5590,7 +5590,7 @@
         <v>13</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.25935931889191</v>
+        <v>1.63680126672291</v>
       </c>
       <c r="AE36" t="n">
         <v>1</v>
@@ -5599,7 +5599,7 @@
         <v>1.17670195598755</v>
       </c>
       <c r="AG36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AH36" t="s">
         <v>45</v>
@@ -5611,7 +5611,7 @@
         <v>46</v>
       </c>
       <c r="AK36" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL36" t="n">
         <v>0</v>
@@ -5620,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="AN36" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO36" t="n">
         <v>2</v>
@@ -5629,7 +5629,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.0044</v>
+        <v>0.0082</v>
       </c>
     </row>
     <row r="37">
@@ -5709,10 +5709,10 @@
         <v>726.89</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.0048120770394548</v>
+        <v>0.00886360905633134</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB37" t="n">
         <v>1.52611586108424</v>
@@ -5721,7 +5721,7 @@
         <v>12</v>
       </c>
       <c r="AD37" t="n">
-        <v>4.06242557442557</v>
+        <v>2.04008907138472</v>
       </c>
       <c r="AE37" t="n">
         <v>1</v>
@@ -5730,7 +5730,7 @@
         <v>1.5989465924308</v>
       </c>
       <c r="AG37" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH37" t="s">
         <v>45</v>
@@ -5742,7 +5742,7 @@
         <v>46</v>
       </c>
       <c r="AK37" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL37" t="n">
         <v>0</v>
@@ -5751,7 +5751,7 @@
         <v>2</v>
       </c>
       <c r="AN37" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO37" t="n">
         <v>2</v>
@@ -5760,7 +5760,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.0048</v>
+        <v>0.0089</v>
       </c>
     </row>
     <row r="38">
@@ -5840,10 +5840,10 @@
         <v>911.153</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.00154153541761186</v>
+        <v>0.00299248647244041</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB38" t="n">
         <v>1.5371310307044</v>
@@ -5852,7 +5852,7 @@
         <v>36</v>
       </c>
       <c r="AD38" t="n">
-        <v>2.7289994109967</v>
+        <v>1.37046249148255</v>
       </c>
       <c r="AE38" t="n">
         <v>1</v>
@@ -5861,7 +5861,7 @@
         <v>1.32666597395516</v>
       </c>
       <c r="AG38" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH38" t="s">
         <v>45</v>
@@ -5873,7 +5873,7 @@
         <v>46</v>
       </c>
       <c r="AK38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL38" t="n">
         <v>0</v>
@@ -5882,7 +5882,7 @@
         <v>2</v>
       </c>
       <c r="AN38" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO38" t="n">
         <v>2</v>
@@ -5891,7 +5891,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.0015</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="39">
@@ -5971,10 +5971,10 @@
         <v>883.226</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.00198908918605463</v>
+        <v>0.00383309961057966</v>
       </c>
       <c r="AA39" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB39" t="n">
         <v>1.53444022924214</v>
@@ -5983,7 +5983,7 @@
         <v>28</v>
       </c>
       <c r="AD39" t="n">
-        <v>2.40873659092972</v>
+        <v>1.20963131630911</v>
       </c>
       <c r="AE39" t="n">
         <v>1</v>
@@ -6004,7 +6004,7 @@
         <v>46</v>
       </c>
       <c r="AK39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL39" t="n">
         <v>0</v>
@@ -6013,7 +6013,7 @@
         <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO39" t="n">
         <v>2</v>
@@ -6022,7 +6022,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.002</v>
+        <v>0.0038</v>
       </c>
     </row>
     <row r="40">
@@ -6102,10 +6102,10 @@
         <v>1271.81</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.0013462281323869</v>
+        <v>0.00262160757142146</v>
       </c>
       <c r="AA40" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB40" t="n">
         <v>1.53470007092107</v>
@@ -6114,7 +6114,7 @@
         <v>41</v>
       </c>
       <c r="AD40" t="n">
-        <v>3.89434118600879</v>
+        <v>1.95567961757511</v>
       </c>
       <c r="AE40" t="n">
         <v>1</v>
@@ -6123,7 +6123,7 @@
         <v>1.32262258176985</v>
       </c>
       <c r="AG40" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH40" t="s">
         <v>45</v>
@@ -6135,7 +6135,7 @@
         <v>46</v>
       </c>
       <c r="AK40" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL40" t="n">
         <v>0</v>
@@ -6144,7 +6144,7 @@
         <v>2</v>
       </c>
       <c r="AN40" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO40" t="n">
         <v>2</v>
@@ -6153,7 +6153,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.0013</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="41">
@@ -6233,10 +6233,10 @@
         <v>990.875</v>
       </c>
       <c r="Z41" t="n">
-        <v>0.00128198998703207</v>
+        <v>0.00249914339305604</v>
       </c>
       <c r="AA41" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AB41" t="n">
         <v>1.53472515590411</v>
@@ -6245,7 +6245,7 @@
         <v>43</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.71557980177791</v>
+        <v>1.8659083369267</v>
       </c>
       <c r="AE41" t="n">
         <v>1</v>
@@ -6254,7 +6254,7 @@
         <v>1.32619097171203</v>
       </c>
       <c r="AG41" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH41" t="s">
         <v>45</v>
@@ -6266,7 +6266,7 @@
         <v>46</v>
       </c>
       <c r="AK41" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL41" t="n">
         <v>0</v>
@@ -6275,7 +6275,7 @@
         <v>2</v>
       </c>
       <c r="AN41" t="n">
-        <v>0.35</v>
+        <v>0.696954349196069</v>
       </c>
       <c r="AO41" t="n">
         <v>2</v>
@@ -6284,7 +6284,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.0013</v>
+        <v>0.0025</v>
       </c>
     </row>
     <row r="42">
@@ -6364,10 +6364,10 @@
         <v>708.824</v>
       </c>
       <c r="Z42" t="n">
-        <v>0.00369838159243507</v>
+        <v>0.00707743447660032</v>
       </c>
       <c r="AA42" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB42" t="n">
         <v>2.1133609099629</v>
@@ -6376,7 +6376,7 @@
         <v>21</v>
       </c>
       <c r="AD42" t="n">
-        <v>4.1327262940634</v>
+        <v>2.06659899798441</v>
       </c>
       <c r="AE42" t="n">
         <v>1</v>
@@ -6385,7 +6385,7 @@
         <v>1.01473868922178</v>
       </c>
       <c r="AG42" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH42" t="s">
         <v>45</v>
@@ -6397,7 +6397,7 @@
         <v>46</v>
       </c>
       <c r="AK42" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AL42" t="n">
         <v>1</v>
@@ -6406,7 +6406,7 @@
         <v>1</v>
       </c>
       <c r="AN42" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO42" t="n">
         <v>2</v>
@@ -6415,7 +6415,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.0037</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="43">
@@ -6495,10 +6495,10 @@
         <v>766.105</v>
       </c>
       <c r="Z43" t="n">
-        <v>0.00309764740870977</v>
+        <v>0.00596978418964176</v>
       </c>
       <c r="AA43" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB43" t="n">
         <v>2.11525065909039</v>
@@ -6507,7 +6507,7 @@
         <v>25</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.76024544484928</v>
+        <v>1.88033731623209</v>
       </c>
       <c r="AE43" t="n">
         <v>1</v>
@@ -6516,7 +6516,7 @@
         <v>1.03922492971639</v>
       </c>
       <c r="AG43" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH43" t="s">
         <v>45</v>
@@ -6537,7 +6537,7 @@
         <v>1</v>
       </c>
       <c r="AN43" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO43" t="n">
         <v>2</v>
@@ -6546,7 +6546,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.0031</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="44">
@@ -6626,10 +6626,10 @@
         <v>932.893</v>
       </c>
       <c r="Z44" t="n">
-        <v>0.00339615995358311</v>
+        <v>0.00642986483553376</v>
       </c>
       <c r="AA44" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB44" t="n">
         <v>1.55253026449514</v>
@@ -6638,7 +6638,7 @@
         <v>17</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.93000217522918</v>
+        <v>1.96522536928515</v>
       </c>
       <c r="AE44" t="n">
         <v>1</v>
@@ -6659,7 +6659,7 @@
         <v>46</v>
       </c>
       <c r="AK44" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL44" t="n">
         <v>0</v>
@@ -6668,7 +6668,7 @@
         <v>2</v>
       </c>
       <c r="AN44" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO44" t="n">
         <v>2</v>
@@ -6677,7 +6677,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.0034</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="45">
@@ -6757,10 +6757,10 @@
         <v>793.696</v>
       </c>
       <c r="Z45" t="n">
-        <v>0.00336760366827271</v>
+        <v>0.00646976641736474</v>
       </c>
       <c r="AA45" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB45" t="n">
         <v>2.11677944862856</v>
@@ -6769,7 +6769,7 @@
         <v>23</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.68281312112896</v>
+        <v>1.84161673537923</v>
       </c>
       <c r="AE45" t="n">
         <v>1</v>
@@ -6790,7 +6790,7 @@
         <v>46</v>
       </c>
       <c r="AK45" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AL45" t="n">
         <v>1</v>
@@ -6799,7 +6799,7 @@
         <v>1</v>
       </c>
       <c r="AN45" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO45" t="n">
         <v>2</v>
@@ -6808,7 +6808,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.0034</v>
+        <v>0.0065</v>
       </c>
     </row>
     <row r="46">
@@ -6888,10 +6888,10 @@
         <v>776.953</v>
       </c>
       <c r="Z46" t="n">
-        <v>0.0029584380673688</v>
+        <v>0.00571061860064608</v>
       </c>
       <c r="AA46" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB46" t="n">
         <v>2.11317004812057</v>
@@ -6900,7 +6900,7 @@
         <v>26</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.83422652722014</v>
+        <v>1.41727501035522</v>
       </c>
       <c r="AE46" t="n">
         <v>1</v>
@@ -6909,10 +6909,10 @@
         <v>1.03659862467219</v>
       </c>
       <c r="AG46" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AH46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI46" t="n">
         <v>2.17293971482224</v>
@@ -6921,7 +6921,7 @@
         <v>46</v>
       </c>
       <c r="AK46" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL46" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>2</v>
       </c>
       <c r="AN46" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO46" t="n">
         <v>2</v>
@@ -6939,7 +6939,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.003</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="47">
@@ -7019,10 +7019,10 @@
         <v>645.479</v>
       </c>
       <c r="Z47" t="n">
-        <v>0.00275635027957215</v>
+        <v>0.00533362306591532</v>
       </c>
       <c r="AA47" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB47" t="n">
         <v>2.11845207201402</v>
@@ -7031,7 +7031,7 @@
         <v>28</v>
       </c>
       <c r="AD47" t="n">
-        <v>2.26653898985849</v>
+        <v>1.13339884425995</v>
       </c>
       <c r="AE47" t="n">
         <v>1</v>
@@ -7040,19 +7040,19 @@
         <v>1.01190264033444</v>
       </c>
       <c r="AG47" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI47" t="n">
         <v>1.68054397677821</v>
       </c>
       <c r="AJ47" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK47" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL47" t="n">
         <v>2</v>
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO47" t="n">
         <v>2</v>
@@ -7070,7 +7070,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0.0028</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="48">
@@ -7150,10 +7150,10 @@
         <v>602.054</v>
       </c>
       <c r="Z48" t="n">
-        <v>0.00411962769594404</v>
+        <v>0.00784601436714543</v>
       </c>
       <c r="AA48" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB48" t="n">
         <v>2.11866567219979</v>
@@ -7162,7 +7162,7 @@
         <v>19</v>
       </c>
       <c r="AD48" t="n">
-        <v>2.17698015362015</v>
+        <v>1.08861431509898</v>
       </c>
       <c r="AE48" t="n">
         <v>1</v>
@@ -7171,10 +7171,10 @@
         <v>1.02247469122928</v>
       </c>
       <c r="AG48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AH48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AI48" t="n">
         <v>1.65058354449738</v>
@@ -7183,7 +7183,7 @@
         <v>46</v>
       </c>
       <c r="AK48" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL48" t="n">
         <v>0</v>
@@ -7192,7 +7192,7 @@
         <v>2</v>
       </c>
       <c r="AN48" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO48" t="n">
         <v>2</v>
@@ -7201,7 +7201,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ48" t="n">
-        <v>0.0041</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="49">
@@ -7281,10 +7281,10 @@
         <v>692.86</v>
       </c>
       <c r="Z49" t="n">
-        <v>0.00138061302400008</v>
+        <v>0.00270000847579789</v>
       </c>
       <c r="AA49" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB49" t="n">
         <v>1.5738988473601</v>
@@ -7293,7 +7293,7 @@
         <v>41</v>
       </c>
       <c r="AD49" t="n">
-        <v>1.22681674883295</v>
+        <v>0.613478387739019</v>
       </c>
       <c r="AE49" t="n">
         <v>1</v>
@@ -7302,7 +7302,7 @@
         <v>2.097059635398</v>
       </c>
       <c r="AG49" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH49" t="s">
         <v>45</v>
@@ -7311,10 +7311,10 @@
         <v>0.675809913418582</v>
       </c>
       <c r="AJ49" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL49" t="n">
         <v>0</v>
@@ -7323,7 +7323,7 @@
         <v>2</v>
       </c>
       <c r="AN49" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO49" t="n">
         <v>2</v>
@@ -7332,7 +7332,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0.0014</v>
+        <v>0.0027</v>
       </c>
     </row>
     <row r="50">
@@ -7412,10 +7412,10 @@
         <v>893.147</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.00144441885330628</v>
+        <v>0.00282150654289767</v>
       </c>
       <c r="AA50" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB50" t="n">
         <v>1.56409927258023</v>
@@ -7424,7 +7424,7 @@
         <v>39</v>
       </c>
       <c r="AD50" t="n">
-        <v>3.24077410461162</v>
+        <v>1.62057200035359</v>
       </c>
       <c r="AE50" t="n">
         <v>1</v>
@@ -7433,7 +7433,7 @@
         <v>1.79263576977403</v>
       </c>
       <c r="AG50" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH50" t="s">
         <v>45</v>
@@ -7445,7 +7445,7 @@
         <v>46</v>
       </c>
       <c r="AK50" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL50" t="n">
         <v>0</v>
@@ -7454,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="AN50" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO50" t="n">
         <v>2</v>
@@ -7463,7 +7463,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.0014</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="51">
@@ -7543,10 +7543,10 @@
         <v>700.373</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.00148938839352634</v>
+        <v>0.00290752167095264</v>
       </c>
       <c r="AA51" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB51" t="n">
         <v>1.57024090631777</v>
@@ -7555,7 +7555,7 @@
         <v>38</v>
       </c>
       <c r="AD51" t="n">
-        <v>1.87108249033304</v>
+        <v>0.935648026152376</v>
       </c>
       <c r="AE51" t="n">
         <v>1</v>
@@ -7564,7 +7564,7 @@
         <v>2.02718591405312</v>
       </c>
       <c r="AG51" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH51" t="s">
         <v>45</v>
@@ -7573,10 +7573,10 @@
         <v>1.02831759289555</v>
       </c>
       <c r="AJ51" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL51" t="n">
         <v>0</v>
@@ -7585,7 +7585,7 @@
         <v>2</v>
       </c>
       <c r="AN51" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO51" t="n">
         <v>2</v>
@@ -7594,7 +7594,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.0015</v>
+        <v>0.0029</v>
       </c>
     </row>
     <row r="52">
@@ -7674,10 +7674,10 @@
         <v>761.961</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.00249792110482677</v>
+        <v>0.00479895132241736</v>
       </c>
       <c r="AA52" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB52" t="n">
         <v>1.57012183731968</v>
@@ -7686,7 +7686,7 @@
         <v>23</v>
       </c>
       <c r="AD52" t="n">
-        <v>3.62972255438516</v>
+        <v>1.8150684221767</v>
       </c>
       <c r="AE52" t="n">
         <v>1</v>
@@ -7695,7 +7695,7 @@
         <v>1.49933418322726</v>
       </c>
       <c r="AG52" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH52" t="s">
         <v>45</v>
@@ -7707,7 +7707,7 @@
         <v>46</v>
       </c>
       <c r="AK52" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL52" t="n">
         <v>0</v>
@@ -7716,7 +7716,7 @@
         <v>2</v>
       </c>
       <c r="AN52" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO52" t="n">
         <v>2</v>
@@ -7725,7 +7725,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ52" t="n">
-        <v>0.0025</v>
+        <v>0.0048</v>
       </c>
     </row>
     <row r="53">
@@ -7805,10 +7805,10 @@
         <v>788.129</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.00256315739240632</v>
+        <v>0.00497092582486781</v>
       </c>
       <c r="AA53" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB53" t="n">
         <v>2.11643567544407</v>
@@ -7817,7 +7817,7 @@
         <v>30</v>
       </c>
       <c r="AD53" t="n">
-        <v>2.1671558864974</v>
+        <v>1.08370162087556</v>
       </c>
       <c r="AE53" t="n">
         <v>1</v>
@@ -7838,7 +7838,7 @@
         <v>46</v>
       </c>
       <c r="AK53" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL53" t="n">
         <v>0</v>
@@ -7847,7 +7847,7 @@
         <v>2</v>
       </c>
       <c r="AN53" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO53" t="n">
         <v>2</v>
@@ -7856,7 +7856,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0.0026</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="54">
@@ -7936,10 +7936,10 @@
         <v>318.682</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.00345512823386535</v>
+        <v>0.00656206442294122</v>
       </c>
       <c r="AA54" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB54" t="n">
         <v>1.67820514216317</v>
@@ -7948,7 +7948,7 @@
         <v>18</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.918344670461625</v>
+        <v>0.459224744330771</v>
       </c>
       <c r="AE54" t="n">
         <v>1</v>
@@ -7957,7 +7957,7 @@
         <v>1.91169796176159</v>
       </c>
       <c r="AG54" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH54" t="s">
         <v>45</v>
@@ -7969,7 +7969,7 @@
         <v>46</v>
       </c>
       <c r="AK54" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL54" t="n">
         <v>0</v>
@@ -7978,7 +7978,7 @@
         <v>2</v>
       </c>
       <c r="AN54" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO54" t="n">
         <v>2</v>
@@ -7987,7 +7987,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ54" t="n">
-        <v>0.0035</v>
+        <v>0.0066</v>
       </c>
     </row>
     <row r="55">
@@ -8067,10 +8067,10 @@
         <v>314.939</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.00203773351738449</v>
+        <v>0.00395967167836002</v>
       </c>
       <c r="AA55" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB55" t="n">
         <v>1.7990275910623</v>
@@ -8079,7 +8079,7 @@
         <v>32</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.38597559864371</v>
+        <v>0.693066895696045</v>
       </c>
       <c r="AE55" t="n">
         <v>1</v>
@@ -8088,7 +8088,7 @@
         <v>1.20587933656296</v>
       </c>
       <c r="AG55" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH55" t="s">
         <v>45</v>
@@ -8100,7 +8100,7 @@
         <v>46</v>
       </c>
       <c r="AK55" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL55" t="n">
         <v>0</v>
@@ -8109,7 +8109,7 @@
         <v>2</v>
       </c>
       <c r="AN55" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO55" t="n">
         <v>2</v>
@@ -8118,7 +8118,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
     </row>
     <row r="56">
@@ -8198,10 +8198,10 @@
         <v>1277.78</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.00285101187575525</v>
+        <v>0.00544352196658367</v>
       </c>
       <c r="AA56" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB56" t="n">
         <v>1.54769216112428</v>
@@ -8210,7 +8210,7 @@
         <v>20</v>
       </c>
       <c r="AD56" t="n">
-        <v>9.5599391608863</v>
+        <v>4.78051515752678</v>
       </c>
       <c r="AE56" t="n">
         <v>1</v>
@@ -8219,7 +8219,7 @@
         <v>1.36032650249707</v>
       </c>
       <c r="AG56" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH56" t="s">
         <v>45</v>
@@ -8231,7 +8231,7 @@
         <v>46</v>
       </c>
       <c r="AK56" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL56" t="n">
         <v>0</v>
@@ -8240,7 +8240,7 @@
         <v>2</v>
       </c>
       <c r="AN56" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO56" t="n">
         <v>2</v>
@@ -8249,7 +8249,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ56" t="n">
-        <v>0.0029</v>
+        <v>0.0054</v>
       </c>
     </row>
     <row r="57">
@@ -8329,10 +8329,10 @@
         <v>829.712</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.00301460965858242</v>
+        <v>0.005741458315726</v>
       </c>
       <c r="AA57" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB57" t="n">
         <v>1.55037068155667</v>
@@ -8341,7 +8341,7 @@
         <v>19</v>
       </c>
       <c r="AD57" t="n">
-        <v>5.91987996039555</v>
+        <v>2.96027782239425</v>
       </c>
       <c r="AE57" t="n">
         <v>1</v>
@@ -8350,7 +8350,7 @@
         <v>1.94195717653816</v>
       </c>
       <c r="AG57" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH57" t="s">
         <v>45</v>
@@ -8362,7 +8362,7 @@
         <v>46</v>
       </c>
       <c r="AK57" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL57" t="n">
         <v>0</v>
@@ -8371,7 +8371,7 @@
         <v>2</v>
       </c>
       <c r="AN57" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO57" t="n">
         <v>2</v>
@@ -8380,7 +8380,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.003</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="58">
@@ -8460,10 +8460,10 @@
         <v>877.905</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.00259864817596358</v>
+        <v>0.00498216041656299</v>
       </c>
       <c r="AA58" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB58" t="n">
         <v>1.55176419650397</v>
@@ -8472,7 +8472,7 @@
         <v>22</v>
       </c>
       <c r="AD58" t="n">
-        <v>6.08399163493418</v>
+        <v>3.04234302536844</v>
       </c>
       <c r="AE58" t="n">
         <v>1</v>
@@ -8481,7 +8481,7 @@
         <v>1.62727996270081</v>
       </c>
       <c r="AG58" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH58" t="s">
         <v>45</v>
@@ -8493,7 +8493,7 @@
         <v>46</v>
       </c>
       <c r="AK58" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL58" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
         <v>2</v>
       </c>
       <c r="AN58" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO58" t="n">
         <v>2</v>
@@ -8511,7 +8511,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.0026</v>
+        <v>0.005</v>
       </c>
     </row>
     <row r="59">
@@ -8591,10 +8591,10 @@
         <v>1006.8</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.00232432507548426</v>
+        <v>0.00450286588478183</v>
       </c>
       <c r="AA59" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB59" t="n">
         <v>1.85281913160031</v>
@@ -8603,7 +8603,7 @@
         <v>29</v>
       </c>
       <c r="AD59" t="n">
-        <v>5.12594705135956</v>
+        <v>2.56326605884302</v>
       </c>
       <c r="AE59" t="n">
         <v>1</v>
@@ -8624,7 +8624,7 @@
         <v>46</v>
       </c>
       <c r="AK59" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL59" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
         <v>2</v>
       </c>
       <c r="AN59" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO59" t="n">
         <v>2</v>
@@ -8642,7 +8642,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ59" t="n">
-        <v>0.0023</v>
+        <v>0.0045</v>
       </c>
     </row>
     <row r="60">
@@ -8722,10 +8722,10 @@
         <v>896.152</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.00360964695634037</v>
+        <v>0.00687473334244572</v>
       </c>
       <c r="AA60" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB60" t="n">
         <v>1.85638986326076</v>
@@ -8734,7 +8734,7 @@
         <v>19</v>
       </c>
       <c r="AD60" t="n">
-        <v>5.63692457280896</v>
+        <v>2.81878398059284</v>
       </c>
       <c r="AE60" t="n">
         <v>1</v>
@@ -8755,7 +8755,7 @@
         <v>46</v>
       </c>
       <c r="AK60" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL60" t="n">
         <v>0</v>
@@ -8764,7 +8764,7 @@
         <v>2</v>
       </c>
       <c r="AN60" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO60" t="n">
         <v>2</v>
@@ -8773,7 +8773,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ60" t="n">
-        <v>0.0036</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="61">
@@ -8853,10 +8853,10 @@
         <v>1128.59</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.00209541021676488</v>
+        <v>0.00407174756614881</v>
       </c>
       <c r="AA61" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB61" t="n">
         <v>1.84994787708671</v>
@@ -8865,7 +8865,7 @@
         <v>32</v>
       </c>
       <c r="AD61" t="n">
-        <v>4.6747222504308</v>
+        <v>2.33762790738726</v>
       </c>
       <c r="AE61" t="n">
         <v>1</v>
@@ -8874,7 +8874,7 @@
         <v>1.66893732869931</v>
       </c>
       <c r="AG61" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH61" t="s">
         <v>45</v>
@@ -8886,7 +8886,7 @@
         <v>46</v>
       </c>
       <c r="AK61" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL61" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>2</v>
       </c>
       <c r="AN61" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO61" t="n">
         <v>2</v>
@@ -8904,7 +8904,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.0021</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="62">
@@ -8984,10 +8984,10 @@
         <v>242.129</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.00370490250198496</v>
+        <v>0.00703644184908966</v>
       </c>
       <c r="AA62" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB62" t="n">
         <v>1.79952407239269</v>
@@ -8996,7 +8996,7 @@
         <v>18</v>
       </c>
       <c r="AD62" t="n">
-        <v>2.23240257731585</v>
+        <v>1.11632868985443</v>
       </c>
       <c r="AE62" t="n">
         <v>1</v>
@@ -9017,7 +9017,7 @@
         <v>46</v>
       </c>
       <c r="AK62" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL62" t="n">
         <v>0</v>
@@ -9026,7 +9026,7 @@
         <v>2</v>
       </c>
       <c r="AN62" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO62" t="n">
         <v>2</v>
@@ -9035,7 +9035,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ62" t="n">
-        <v>0.0037</v>
+        <v>0.007</v>
       </c>
     </row>
     <row r="63">
@@ -9115,10 +9115,10 @@
         <v>1035.53</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.00295501960236676</v>
+        <v>0.00567711894548834</v>
       </c>
       <c r="AA63" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB63" t="n">
         <v>1.85744089291625</v>
@@ -9127,7 +9127,7 @@
         <v>23</v>
       </c>
       <c r="AD63" t="n">
-        <v>6.6260834978314</v>
+        <v>3.31341989350949</v>
       </c>
       <c r="AE63" t="n">
         <v>1</v>
@@ -9136,7 +9136,7 @@
         <v>1.17761673943414</v>
       </c>
       <c r="AG63" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH63" t="s">
         <v>45</v>
@@ -9148,7 +9148,7 @@
         <v>46</v>
       </c>
       <c r="AK63" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL63" t="n">
         <v>0</v>
@@ -9157,7 +9157,7 @@
         <v>2</v>
       </c>
       <c r="AN63" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO63" t="n">
         <v>2</v>
@@ -9166,7 +9166,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ63" t="n">
-        <v>0.003</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="64">
@@ -9246,10 +9246,10 @@
         <v>954.496</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.00413853248671681</v>
+        <v>0.00774408404367912</v>
       </c>
       <c r="AA64" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB64" t="n">
         <v>1.54899358788543</v>
@@ -9258,7 +9258,7 @@
         <v>14</v>
       </c>
       <c r="AD64" t="n">
-        <v>9.2302693877551</v>
+        <v>4.61566145700532</v>
       </c>
       <c r="AE64" t="n">
         <v>1</v>
@@ -9267,7 +9267,7 @@
         <v>1.20950646656515</v>
       </c>
       <c r="AG64" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH64" t="s">
         <v>45</v>
@@ -9279,7 +9279,7 @@
         <v>46</v>
       </c>
       <c r="AK64" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL64" t="n">
         <v>0</v>
@@ -9288,7 +9288,7 @@
         <v>2</v>
       </c>
       <c r="AN64" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO64" t="n">
         <v>2</v>
@@ -9297,7 +9297,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ64" t="n">
-        <v>0.0041</v>
+        <v>0.0077</v>
       </c>
     </row>
     <row r="65">
@@ -9377,10 +9377,10 @@
         <v>609.609</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.00361025582143778</v>
+        <v>0.00687589295313254</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB65" t="n">
         <v>1.85670299388229</v>
@@ -9389,7 +9389,7 @@
         <v>19</v>
       </c>
       <c r="AD65" t="n">
-        <v>1.78612401081222</v>
+        <v>0.893163937888359</v>
       </c>
       <c r="AE65" t="n">
         <v>1</v>
@@ -9398,7 +9398,7 @@
         <v>2.30666028863106</v>
       </c>
       <c r="AG65" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH65" t="s">
         <v>45</v>
@@ -9407,10 +9407,10 @@
         <v>1.16070562941203</v>
       </c>
       <c r="AJ65" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK65" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL65" t="n">
         <v>0</v>
@@ -9419,7 +9419,7 @@
         <v>2</v>
       </c>
       <c r="AN65" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO65" t="n">
         <v>2</v>
@@ -9428,7 +9428,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.0036</v>
+        <v>0.0069</v>
       </c>
     </row>
     <row r="66">
@@ -9508,10 +9508,10 @@
         <v>817.009</v>
       </c>
       <c r="Z66" t="n">
-        <v>0.00298802130759627</v>
+        <v>0.00569231720157645</v>
       </c>
       <c r="AA66" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB66" t="n">
         <v>1.54523387621407</v>
@@ -9520,7 +9520,7 @@
         <v>19</v>
       </c>
       <c r="AD66" t="n">
-        <v>4.39350275689223</v>
+        <v>2.19700211167576</v>
       </c>
       <c r="AE66" t="n">
         <v>1</v>
@@ -9529,7 +9529,7 @@
         <v>1.41590645442212</v>
       </c>
       <c r="AG66" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH66" t="s">
         <v>45</v>
@@ -9541,7 +9541,7 @@
         <v>46</v>
       </c>
       <c r="AK66" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL66" t="n">
         <v>0</v>
@@ -9550,7 +9550,7 @@
         <v>2</v>
       </c>
       <c r="AN66" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO66" t="n">
         <v>2</v>
@@ -9559,7 +9559,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.003</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="67">
@@ -9639,10 +9639,10 @@
         <v>1209.76</v>
       </c>
       <c r="Z67" t="n">
-        <v>0.00299718337846222</v>
+        <v>0.00570826918935819</v>
       </c>
       <c r="AA67" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB67" t="n">
         <v>1.54140859463771</v>
@@ -9651,7 +9651,7 @@
         <v>19</v>
       </c>
       <c r="AD67" t="n">
-        <v>7.26374666805304</v>
+        <v>3.63228786948085</v>
       </c>
       <c r="AE67" t="n">
         <v>1</v>
@@ -9660,7 +9660,7 @@
         <v>1.13564661758505</v>
       </c>
       <c r="AG67" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH67" t="s">
         <v>45</v>
@@ -9672,7 +9672,7 @@
         <v>46</v>
       </c>
       <c r="AK67" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL67" t="n">
         <v>0</v>
@@ -9681,7 +9681,7 @@
         <v>2</v>
       </c>
       <c r="AN67" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO67" t="n">
         <v>2</v>
@@ -9690,7 +9690,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ67" t="n">
-        <v>0.003</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="68">
@@ -9770,10 +9770,10 @@
         <v>1274.68</v>
       </c>
       <c r="Z68" t="n">
-        <v>0.00237020428954655</v>
+        <v>0.0045606288892104</v>
       </c>
       <c r="AA68" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AB68" t="n">
         <v>1.55079080658903</v>
@@ -9782,7 +9782,7 @@
         <v>24</v>
       </c>
       <c r="AD68" t="n">
-        <v>9.57481966821991</v>
+        <v>4.78795626041069</v>
       </c>
       <c r="AE68" t="n">
         <v>1</v>
@@ -9791,7 +9791,7 @@
         <v>1.11528106664191</v>
       </c>
       <c r="AG68" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH68" t="s">
         <v>45</v>
@@ -9803,7 +9803,7 @@
         <v>46</v>
       </c>
       <c r="AK68" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL68" t="n">
         <v>0</v>
@@ -9812,7 +9812,7 @@
         <v>2</v>
       </c>
       <c r="AN68" t="n">
-        <v>0.35</v>
+        <v>0.699920112384134</v>
       </c>
       <c r="AO68" t="n">
         <v>2</v>
@@ -9821,7 +9821,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0.0024</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="69">
@@ -9901,10 +9901,10 @@
         <v>725.726</v>
       </c>
       <c r="Z69" t="n">
-        <v>0.00302688863026471</v>
+        <v>0.0101773926800338</v>
       </c>
       <c r="AA69" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB69" t="n">
         <v>1.57398208773765</v>
@@ -9913,7 +9913,7 @@
         <v>183</v>
       </c>
       <c r="AD69" t="n">
-        <v>3.38322784194615</v>
+        <v>1.00621585609761</v>
       </c>
       <c r="AE69" t="n">
         <v>1</v>
@@ -9934,7 +9934,7 @@
         <v>46</v>
       </c>
       <c r="AK69" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL69" t="n">
         <v>0</v>
@@ -9943,7 +9943,7 @@
         <v>2</v>
       </c>
       <c r="AN69" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO69" t="n">
         <v>2</v>
@@ -9952,7 +9952,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ69" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="70">
@@ -10032,10 +10032,10 @@
         <v>745.67</v>
       </c>
       <c r="Z70" t="n">
-        <v>0.00156933894513814</v>
+        <v>0.00527663242480916</v>
       </c>
       <c r="AA70" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB70" t="n">
         <v>1.57382277069568</v>
@@ -10044,7 +10044,7 @@
         <v>353</v>
       </c>
       <c r="AD70" t="n">
-        <v>2.03049035084107</v>
+        <v>0.603894175065139</v>
       </c>
       <c r="AE70" t="n">
         <v>1</v>
@@ -10053,7 +10053,7 @@
         <v>1.53480766131497</v>
       </c>
       <c r="AG70" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH70" t="s">
         <v>45</v>
@@ -10065,7 +10065,7 @@
         <v>46</v>
       </c>
       <c r="AK70" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL70" t="n">
         <v>0</v>
@@ -10074,7 +10074,7 @@
         <v>2</v>
       </c>
       <c r="AN70" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO70" t="n">
         <v>2</v>
@@ -10083,7 +10083,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ70" t="n">
-        <v>0.0016</v>
+        <v>0.0053</v>
       </c>
     </row>
     <row r="71">
@@ -10163,10 +10163,10 @@
         <v>1042.55</v>
       </c>
       <c r="Z71" t="n">
-        <v>0.00282783617920953</v>
+        <v>0.00950811303160005</v>
       </c>
       <c r="AA71" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB71" t="n">
         <v>1.57550872841674</v>
@@ -10175,7 +10175,7 @@
         <v>196</v>
       </c>
       <c r="AD71" t="n">
-        <v>5.90537883405753</v>
+        <v>1.75633628495851</v>
       </c>
       <c r="AE71" t="n">
         <v>1</v>
@@ -10196,7 +10196,7 @@
         <v>46</v>
       </c>
       <c r="AK71" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL71" t="n">
         <v>0</v>
@@ -10205,7 +10205,7 @@
         <v>2</v>
       </c>
       <c r="AN71" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO71" t="n">
         <v>2</v>
@@ -10214,7 +10214,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ71" t="n">
-        <v>0.0028</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="72">
@@ -10294,10 +10294,10 @@
         <v>859.798</v>
       </c>
       <c r="Z72" t="n">
-        <v>0.00188832452513965</v>
+        <v>0.00634916660214354</v>
       </c>
       <c r="AA72" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB72" t="n">
         <v>1.57540217525937</v>
@@ -10306,7 +10306,7 @@
         <v>293</v>
       </c>
       <c r="AD72" t="n">
-        <v>3.00509966355897</v>
+        <v>0.893755629797385</v>
       </c>
       <c r="AE72" t="n">
         <v>1</v>
@@ -10327,7 +10327,7 @@
         <v>46</v>
       </c>
       <c r="AK72" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL72" t="n">
         <v>0</v>
@@ -10336,7 +10336,7 @@
         <v>2</v>
       </c>
       <c r="AN72" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO72" t="n">
         <v>2</v>
@@ -10345,7 +10345,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.0019</v>
+        <v>0.0063</v>
       </c>
     </row>
     <row r="73">
@@ -10425,10 +10425,10 @@
         <v>308.848</v>
       </c>
       <c r="Z73" t="n">
-        <v>0.00276693313537507</v>
+        <v>0.00930333701628351</v>
       </c>
       <c r="AA73" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB73" t="n">
         <v>1.40718313741932</v>
@@ -10437,7 +10437,7 @@
         <v>179</v>
       </c>
       <c r="AD73" t="n">
-        <v>0.976914633627703</v>
+        <v>0.290547087081352</v>
       </c>
       <c r="AE73" t="n">
         <v>1</v>
@@ -10446,19 +10446,19 @@
         <v>1.08818374964771</v>
       </c>
       <c r="AG73" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI73" t="n">
         <v>-0.481144229698678</v>
       </c>
       <c r="AJ73" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK73" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL73" t="n">
         <v>2</v>
@@ -10467,7 +10467,7 @@
         <v>0</v>
       </c>
       <c r="AN73" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO73" t="n">
         <v>2</v>
@@ -10476,7 +10476,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ73" t="n">
-        <v>0.0028</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="74">
@@ -10556,10 +10556,10 @@
         <v>622.843</v>
       </c>
       <c r="Z74" t="n">
-        <v>0.00351063722090437</v>
+        <v>0.011803914156948</v>
       </c>
       <c r="AA74" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB74" t="n">
         <v>1.56474116131738</v>
@@ -10568,7 +10568,7 @@
         <v>157</v>
       </c>
       <c r="AD74" t="n">
-        <v>3.53630913771851</v>
+        <v>1.05174421962323</v>
       </c>
       <c r="AE74" t="n">
         <v>1</v>
@@ -10589,7 +10589,7 @@
         <v>46</v>
       </c>
       <c r="AK74" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL74" t="n">
         <v>0</v>
@@ -10598,7 +10598,7 @@
         <v>2</v>
       </c>
       <c r="AN74" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO74" t="n">
         <v>2</v>
@@ -10607,7 +10607,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ74" t="n">
-        <v>0.0035</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="75">
@@ -10687,10 +10687,10 @@
         <v>721.763</v>
       </c>
       <c r="Z75" t="n">
-        <v>0.00216918251712115</v>
+        <v>0.00729350331910809</v>
       </c>
       <c r="AA75" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB75" t="n">
         <v>1.56800907666186</v>
@@ -10699,7 +10699,7 @@
         <v>254</v>
       </c>
       <c r="AD75" t="n">
-        <v>3.24095968264383</v>
+        <v>0.963903459653903</v>
       </c>
       <c r="AE75" t="n">
         <v>1</v>
@@ -10708,7 +10708,7 @@
         <v>1.22927981864376</v>
       </c>
       <c r="AG75" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH75" t="s">
         <v>45</v>
@@ -10720,7 +10720,7 @@
         <v>46</v>
       </c>
       <c r="AK75" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL75" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
         <v>2</v>
       </c>
       <c r="AN75" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO75" t="n">
         <v>2</v>
@@ -10738,7 +10738,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ75" t="n">
-        <v>0.0022</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="76">
@@ -10818,10 +10818,10 @@
         <v>128.55</v>
       </c>
       <c r="Z76" t="n">
-        <v>0.00243393157721043</v>
+        <v>0.00818367652180133</v>
       </c>
       <c r="AA76" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB76" t="n">
         <v>1.75938482581211</v>
@@ -10830,7 +10830,7 @@
         <v>255</v>
       </c>
       <c r="AD76" t="n">
-        <v>2.35699298666981</v>
+        <v>0.70100029518963</v>
       </c>
       <c r="AE76" t="n">
         <v>1</v>
@@ -10839,7 +10839,7 @@
         <v>1.560455147584</v>
       </c>
       <c r="AG76" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH76" t="s">
         <v>45</v>
@@ -10851,7 +10851,7 @@
         <v>46</v>
       </c>
       <c r="AK76" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL76" t="n">
         <v>0</v>
@@ -10860,7 +10860,7 @@
         <v>2</v>
       </c>
       <c r="AN76" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO76" t="n">
         <v>2</v>
@@ -10869,7 +10869,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0.0024</v>
+        <v>0.0082</v>
       </c>
     </row>
     <row r="77">
@@ -10949,10 +10949,10 @@
         <v>729.028</v>
       </c>
       <c r="Z77" t="n">
-        <v>0.00297398052890835</v>
+        <v>0.0099994982844242</v>
       </c>
       <c r="AA77" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB77" t="n">
         <v>1.87785627682499</v>
@@ -10961,7 +10961,7 @@
         <v>222</v>
       </c>
       <c r="AD77" t="n">
-        <v>3.70044142842251</v>
+        <v>1.10055929242335</v>
       </c>
       <c r="AE77" t="n">
         <v>1</v>
@@ -10982,7 +10982,7 @@
         <v>46</v>
       </c>
       <c r="AK77" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL77" t="n">
         <v>0</v>
@@ -10991,7 +10991,7 @@
         <v>2</v>
       </c>
       <c r="AN77" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO77" t="n">
         <v>2</v>
@@ -11000,7 +11000,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="78">
@@ -11080,10 +11080,10 @@
         <v>794.601</v>
       </c>
       <c r="Z78" t="n">
-        <v>0.00275849547478179</v>
+        <v>0.00927496683302007</v>
       </c>
       <c r="AA78" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB78" t="n">
         <v>1.87577692285162</v>
@@ -11092,7 +11092,7 @@
         <v>239</v>
       </c>
       <c r="AD78" t="n">
-        <v>4.15703023736609</v>
+        <v>1.23635472824344</v>
       </c>
       <c r="AE78" t="n">
         <v>1</v>
@@ -11113,7 +11113,7 @@
         <v>46</v>
       </c>
       <c r="AK78" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL78" t="n">
         <v>0</v>
@@ -11122,7 +11122,7 @@
         <v>2</v>
       </c>
       <c r="AN78" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO78" t="n">
         <v>2</v>
@@ -11131,7 +11131,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.0028</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="79">
@@ -11211,10 +11211,10 @@
         <v>662.23</v>
       </c>
       <c r="Z79" t="n">
-        <v>0.0029484508838058</v>
+        <v>0.00991365924145689</v>
       </c>
       <c r="AA79" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB79" t="n">
         <v>1.57531518649053</v>
@@ -11223,7 +11223,7 @@
         <v>188</v>
       </c>
       <c r="AD79" t="n">
-        <v>3.37788150041135</v>
+        <v>1.00462578475872</v>
       </c>
       <c r="AE79" t="n">
         <v>1</v>
@@ -11235,25 +11235,25 @@
         <v>44</v>
       </c>
       <c r="AH79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI79" t="n">
-        <v>1.8624298090172</v>
+        <v>1.89033960421566</v>
       </c>
       <c r="AJ79" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK79" t="s">
         <v>51</v>
       </c>
-      <c r="AK79" t="s">
-        <v>52</v>
-      </c>
       <c r="AL79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN79" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO79" t="n">
         <v>2</v>
@@ -11262,7 +11262,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ79" t="n">
-        <v>0.0029</v>
+        <v>0.0099</v>
       </c>
     </row>
     <row r="80">
@@ -11342,10 +11342,10 @@
         <v>659.168</v>
       </c>
       <c r="Z80" t="n">
-        <v>0.00355486843071517</v>
+        <v>0.0119526339963423</v>
       </c>
       <c r="AA80" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB80" t="n">
         <v>1.57429887645958</v>
@@ -11354,7 +11354,7 @@
         <v>155</v>
       </c>
       <c r="AD80" t="n">
-        <v>3.18531706081936</v>
+        <v>0.947354621984603</v>
       </c>
       <c r="AE80" t="n">
         <v>1</v>
@@ -11363,7 +11363,7 @@
         <v>1.05891409263933</v>
       </c>
       <c r="AG80" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH80" t="s">
         <v>45</v>
@@ -11375,7 +11375,7 @@
         <v>46</v>
       </c>
       <c r="AK80" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL80" t="n">
         <v>0</v>
@@ -11384,7 +11384,7 @@
         <v>2</v>
       </c>
       <c r="AN80" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO80" t="n">
         <v>2</v>
@@ -11393,7 +11393,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ80" t="n">
-        <v>0.0036</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="81">
@@ -11473,10 +11473,10 @@
         <v>736.707</v>
       </c>
       <c r="Z81" t="n">
-        <v>0.00273901372280977</v>
+        <v>0.00920946279103721</v>
       </c>
       <c r="AA81" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB81" t="n">
         <v>1.57297645224218</v>
@@ -11485,7 +11485,7 @@
         <v>202</v>
       </c>
       <c r="AD81" t="n">
-        <v>3.36120098797601</v>
+        <v>0.999664783938086</v>
       </c>
       <c r="AE81" t="n">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>46</v>
       </c>
       <c r="AK81" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL81" t="n">
         <v>0</v>
@@ -11515,7 +11515,7 @@
         <v>2</v>
       </c>
       <c r="AN81" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO81" t="n">
         <v>2</v>
@@ -11524,7 +11524,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.0027</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="82">
@@ -11604,10 +11604,10 @@
         <v>612.268</v>
       </c>
       <c r="Z82" t="n">
-        <v>0.00357769154058279</v>
+        <v>0.0120293727798509</v>
       </c>
       <c r="AA82" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB82" t="n">
         <v>1.57418427785643</v>
@@ -11616,7 +11616,7 @@
         <v>154</v>
       </c>
       <c r="AD82" t="n">
-        <v>3.38176731807092</v>
+        <v>1.00578147734746</v>
       </c>
       <c r="AE82" t="n">
         <v>1</v>
@@ -11625,7 +11625,7 @@
         <v>1.00975075013473</v>
       </c>
       <c r="AG82" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH82" t="s">
         <v>45</v>
@@ -11634,10 +11634,10 @@
         <v>1.86323373021658</v>
       </c>
       <c r="AJ82" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK82" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL82" t="n">
         <v>2</v>
@@ -11646,7 +11646,7 @@
         <v>0</v>
       </c>
       <c r="AN82" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO82" t="n">
         <v>2</v>
@@ -11655,7 +11655,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ82" t="n">
-        <v>0.0036</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="83">
@@ -11735,10 +11735,10 @@
         <v>549.389</v>
       </c>
       <c r="Z83" t="n">
-        <v>0.00377011135457205</v>
+        <v>0.0126763513263382</v>
       </c>
       <c r="AA83" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB83" t="n">
         <v>1.57267502219291</v>
@@ -11747,7 +11747,7 @@
         <v>147</v>
       </c>
       <c r="AD83" t="n">
-        <v>2.39904011148339</v>
+        <v>0.713505655652258</v>
       </c>
       <c r="AE83" t="n">
         <v>1</v>
@@ -11759,7 +11759,7 @@
         <v>44</v>
       </c>
       <c r="AH83" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI83" t="n">
         <v>1.50733649414636</v>
@@ -11768,7 +11768,7 @@
         <v>46</v>
       </c>
       <c r="AK83" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL83" t="n">
         <v>0</v>
@@ -11777,7 +11777,7 @@
         <v>2</v>
       </c>
       <c r="AN83" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO83" t="n">
         <v>2</v>
@@ -11786,7 +11786,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0.0038</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="84">
@@ -11866,10 +11866,10 @@
         <v>808.049</v>
       </c>
       <c r="Z84" t="n">
-        <v>0.0016419604705793</v>
+        <v>0.00552080982005516</v>
       </c>
       <c r="AA84" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB84" t="n">
         <v>1.5715907361259</v>
@@ -11878,7 +11878,7 @@
         <v>336</v>
       </c>
       <c r="AD84" t="n">
-        <v>2.60067625219728</v>
+        <v>0.773474860041382</v>
       </c>
       <c r="AE84" t="n">
         <v>1</v>
@@ -11899,7 +11899,7 @@
         <v>46</v>
       </c>
       <c r="AK84" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL84" t="n">
         <v>0</v>
@@ -11908,7 +11908,7 @@
         <v>2</v>
       </c>
       <c r="AN84" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO84" t="n">
         <v>2</v>
@@ -11917,7 +11917,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0.0016</v>
+        <v>0.0055</v>
       </c>
     </row>
     <row r="85">
@@ -11997,10 +11997,10 @@
         <v>560.621</v>
       </c>
       <c r="Z85" t="n">
-        <v>0.00329378421487243</v>
+        <v>0.0110747832024207</v>
       </c>
       <c r="AA85" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB85" t="n">
         <v>1.57160561109627</v>
@@ -12009,7 +12009,7 @@
         <v>168</v>
       </c>
       <c r="AD85" t="n">
-        <v>2.32418484459926</v>
+        <v>0.691242728066542</v>
       </c>
       <c r="AE85" t="n">
         <v>1</v>
@@ -12030,7 +12030,7 @@
         <v>46</v>
       </c>
       <c r="AK85" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL85" t="n">
         <v>0</v>
@@ -12039,7 +12039,7 @@
         <v>2</v>
       </c>
       <c r="AN85" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO85" t="n">
         <v>2</v>
@@ -12048,7 +12048,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ85" t="n">
-        <v>0.0033</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="86">
@@ -12128,10 +12128,10 @@
         <v>613.195</v>
       </c>
       <c r="Z86" t="n">
-        <v>0.00396005479951046</v>
+        <v>0.0133150035075939</v>
       </c>
       <c r="AA86" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB86" t="n">
         <v>1.57270747751987</v>
@@ -12140,7 +12140,7 @@
         <v>140</v>
       </c>
       <c r="AD86" t="n">
-        <v>3.32142302076364</v>
+        <v>0.987834300387386</v>
       </c>
       <c r="AE86" t="n">
         <v>1</v>
@@ -12152,7 +12152,7 @@
         <v>44</v>
       </c>
       <c r="AH86" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI86" t="n">
         <v>1.89467732207738</v>
@@ -12161,7 +12161,7 @@
         <v>46</v>
       </c>
       <c r="AK86" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL86" t="n">
         <v>0</v>
@@ -12170,7 +12170,7 @@
         <v>2</v>
       </c>
       <c r="AN86" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO86" t="n">
         <v>2</v>
@@ -12179,7 +12179,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ86" t="n">
-        <v>0.004</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="87">
@@ -12259,10 +12259,10 @@
         <v>271.495</v>
       </c>
       <c r="Z87" t="n">
-        <v>0.00272706027335845</v>
+        <v>0.00916927137212252</v>
       </c>
       <c r="AA87" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB87" t="n">
         <v>1.90115059056989</v>
@@ -12271,7 +12271,7 @@
         <v>245</v>
       </c>
       <c r="AD87" t="n">
-        <v>1.44984052677376</v>
+        <v>0.431201383709791</v>
       </c>
       <c r="AE87" t="n">
         <v>1</v>
@@ -12280,19 +12280,19 @@
         <v>1.19320023822693</v>
       </c>
       <c r="AG87" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI87" t="n">
         <v>-0.964727810797832</v>
       </c>
       <c r="AJ87" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK87" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL87" t="n">
         <v>2</v>
@@ -12301,7 +12301,7 @@
         <v>0</v>
       </c>
       <c r="AN87" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO87" t="n">
         <v>2</v>
@@ -12310,7 +12310,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ87" t="n">
-        <v>0.0027</v>
+        <v>0.0092</v>
       </c>
     </row>
     <row r="88">
@@ -12390,10 +12390,10 @@
         <v>567.42</v>
       </c>
       <c r="Z88" t="n">
-        <v>0.00341599089562682</v>
+        <v>0.0114856821584395</v>
       </c>
       <c r="AA88" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB88" t="n">
         <v>1.57135581198834</v>
@@ -12402,7 +12402,7 @@
         <v>161</v>
       </c>
       <c r="AD88" t="n">
-        <v>2.82974769956292</v>
+        <v>0.841603680589853</v>
       </c>
       <c r="AE88" t="n">
         <v>1</v>
@@ -12423,7 +12423,7 @@
         <v>46</v>
       </c>
       <c r="AK88" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL88" t="n">
         <v>0</v>
@@ -12432,7 +12432,7 @@
         <v>2</v>
       </c>
       <c r="AN88" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO88" t="n">
         <v>2</v>
@@ -12441,7 +12441,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ88" t="n">
-        <v>0.0034</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="89">
@@ -12521,10 +12521,10 @@
         <v>675.568</v>
       </c>
       <c r="Z89" t="n">
-        <v>0.00305171361415601</v>
+        <v>0.0102608624208136</v>
       </c>
       <c r="AA89" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB89" t="n">
         <v>1.56945271585166</v>
@@ -12533,7 +12533,7 @@
         <v>181</v>
       </c>
       <c r="AD89" t="n">
-        <v>3.8993547413781</v>
+        <v>1.15971869250965</v>
       </c>
       <c r="AE89" t="n">
         <v>1</v>
@@ -12554,7 +12554,7 @@
         <v>46</v>
       </c>
       <c r="AK89" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL89" t="n">
         <v>0</v>
@@ -12563,7 +12563,7 @@
         <v>2</v>
       </c>
       <c r="AN89" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO89" t="n">
         <v>2</v>
@@ -12572,7 +12572,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ89" t="n">
-        <v>0.0031</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="90">
@@ -12652,10 +12652,10 @@
         <v>1044.27</v>
       </c>
       <c r="Z90" t="n">
-        <v>0.00129769231594219</v>
+        <v>0.00458758853527239</v>
       </c>
       <c r="AA90" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB90" t="n">
         <v>1.57947693311821</v>
@@ -12664,7 +12664,7 @@
         <v>428</v>
       </c>
       <c r="AD90" t="n">
-        <v>2.50962799693178</v>
+        <v>0.709899098938784</v>
       </c>
       <c r="AE90" t="n">
         <v>1</v>
@@ -12673,7 +12673,7 @@
         <v>1.67105935826976</v>
       </c>
       <c r="AG90" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH90" t="s">
         <v>45</v>
@@ -12685,7 +12685,7 @@
         <v>46</v>
       </c>
       <c r="AK90" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL90" t="n">
         <v>0</v>
@@ -12694,7 +12694,7 @@
         <v>2</v>
       </c>
       <c r="AN90" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO90" t="n">
         <v>2</v>
@@ -12703,7 +12703,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.0013</v>
+        <v>0.0046</v>
       </c>
     </row>
     <row r="91">
@@ -12783,10 +12783,10 @@
         <v>915.433</v>
       </c>
       <c r="Z91" t="n">
-        <v>0.00200343862635197</v>
+        <v>0.00708253563688634</v>
       </c>
       <c r="AA91" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB91" t="n">
         <v>1.57985445963755</v>
@@ -12795,7 +12795,7 @@
         <v>277</v>
       </c>
       <c r="AD91" t="n">
-        <v>4.11697352691832</v>
+        <v>1.16456933086788</v>
       </c>
       <c r="AE91" t="n">
         <v>1</v>
@@ -12804,7 +12804,7 @@
         <v>1.19595135340843</v>
       </c>
       <c r="AG91" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH91" t="s">
         <v>45</v>
@@ -12816,7 +12816,7 @@
         <v>46</v>
       </c>
       <c r="AK91" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL91" t="n">
         <v>0</v>
@@ -12825,7 +12825,7 @@
         <v>2</v>
       </c>
       <c r="AN91" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO91" t="n">
         <v>2</v>
@@ -12834,7 +12834,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ91" t="n">
-        <v>0.002</v>
+        <v>0.0071</v>
       </c>
     </row>
     <row r="92">
@@ -12914,10 +12914,10 @@
         <v>818.785</v>
       </c>
       <c r="Z92" t="n">
-        <v>0.00482870020176631</v>
+        <v>0.0162356743476342</v>
       </c>
       <c r="AA92" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB92" t="n">
         <v>1.57277663714674</v>
@@ -12926,7 +12926,7 @@
         <v>115</v>
       </c>
       <c r="AD92" t="n">
-        <v>4.76029742428899</v>
+        <v>1.41577421676244</v>
       </c>
       <c r="AE92" t="n">
         <v>1</v>
@@ -12938,7 +12938,7 @@
         <v>44</v>
       </c>
       <c r="AH92" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI92" t="n">
         <v>2.66639402686783</v>
@@ -12947,16 +12947,16 @@
         <v>46</v>
       </c>
       <c r="AK92" t="s">
-        <v>95</v>
+        <v>44</v>
       </c>
       <c r="AL92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN92" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO92" t="n">
         <v>2</v>
@@ -12965,7 +12965,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ92" t="n">
-        <v>0.0048</v>
+        <v>0.016</v>
       </c>
     </row>
     <row r="93">
@@ -13045,10 +13045,10 @@
         <v>1130.91</v>
       </c>
       <c r="Z93" t="n">
-        <v>0.00273734659613411</v>
+        <v>0.00967703954721662</v>
       </c>
       <c r="AA93" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB93" t="n">
         <v>1.57984003548311</v>
@@ -13057,7 +13057,7 @@
         <v>203</v>
       </c>
       <c r="AD93" t="n">
-        <v>7.07746098460221</v>
+        <v>2.00200315819161</v>
       </c>
       <c r="AE93" t="n">
         <v>1</v>
@@ -13078,7 +13078,7 @@
         <v>46</v>
       </c>
       <c r="AK93" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL93" t="n">
         <v>0</v>
@@ -13087,7 +13087,7 @@
         <v>2</v>
       </c>
       <c r="AN93" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO93" t="n">
         <v>2</v>
@@ -13096,7 +13096,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.0027</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="94">
@@ -13176,10 +13176,10 @@
         <v>1227.73</v>
       </c>
       <c r="Z94" t="n">
-        <v>0.0017312370741117</v>
+        <v>0.00612025150759014</v>
       </c>
       <c r="AA94" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB94" t="n">
         <v>1.57789893326181</v>
@@ -13188,7 +13188,7 @@
         <v>321</v>
       </c>
       <c r="AD94" t="n">
-        <v>4.38301356579797</v>
+        <v>1.23982414317999</v>
       </c>
       <c r="AE94" t="n">
         <v>1</v>
@@ -13197,7 +13197,7 @@
         <v>1.14406596542069</v>
       </c>
       <c r="AG94" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH94" t="s">
         <v>45</v>
@@ -13209,7 +13209,7 @@
         <v>46</v>
       </c>
       <c r="AK94" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL94" t="n">
         <v>0</v>
@@ -13218,7 +13218,7 @@
         <v>2</v>
       </c>
       <c r="AN94" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO94" t="n">
         <v>2</v>
@@ -13227,7 +13227,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ94" t="n">
-        <v>0.0017</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="95">
@@ -13307,10 +13307,10 @@
         <v>740.079</v>
       </c>
       <c r="Z95" t="n">
-        <v>0.00430796461060795</v>
+        <v>0.01448479043975</v>
       </c>
       <c r="AA95" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB95" t="n">
         <v>1.57548420045091</v>
@@ -13319,7 +13319,7 @@
         <v>128</v>
       </c>
       <c r="AD95" t="n">
-        <v>4.37745478490334</v>
+        <v>1.3019118485932</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -13331,7 +13331,7 @@
         <v>44</v>
       </c>
       <c r="AH95" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI95" t="n">
         <v>2.45320992908795</v>
@@ -13340,7 +13340,7 @@
         <v>46</v>
       </c>
       <c r="AK95" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL95" t="n">
         <v>0</v>
@@ -13349,7 +13349,7 @@
         <v>2</v>
       </c>
       <c r="AN95" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO95" t="n">
         <v>2</v>
@@ -13358,7 +13358,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ95" t="n">
-        <v>0.0043</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="96">
@@ -13438,10 +13438,10 @@
         <v>947.41</v>
       </c>
       <c r="Z96" t="n">
-        <v>0.00353735771540102</v>
+        <v>0.0118937572262892</v>
       </c>
       <c r="AA96" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB96" t="n">
         <v>1.57665086743589</v>
@@ -13450,7 +13450,7 @@
         <v>157</v>
       </c>
       <c r="AD96" t="n">
-        <v>7.92082098016466</v>
+        <v>2.3557549286919</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -13459,7 +13459,7 @@
         <v>1.01272277882202</v>
       </c>
       <c r="AG96" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH96" t="s">
         <v>45</v>
@@ -13468,10 +13468,10 @@
         <v>4.37092924421334</v>
       </c>
       <c r="AJ96" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK96" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL96" t="n">
         <v>2</v>
@@ -13480,7 +13480,7 @@
         <v>0</v>
       </c>
       <c r="AN96" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO96" t="n">
         <v>2</v>
@@ -13489,7 +13489,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ96" t="n">
-        <v>0.0035</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="97">
@@ -13569,10 +13569,10 @@
         <v>856.73</v>
       </c>
       <c r="Z97" t="n">
-        <v>0.00402469689617636</v>
+        <v>0.0135323514452919</v>
       </c>
       <c r="AA97" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB97" t="n">
         <v>1.57538135650332</v>
@@ -13581,7 +13581,7 @@
         <v>138</v>
       </c>
       <c r="AD97" t="n">
-        <v>6.27980191941311</v>
+        <v>1.86769456851918</v>
       </c>
       <c r="AE97" t="n">
         <v>1</v>
@@ -13602,7 +13602,7 @@
         <v>46</v>
       </c>
       <c r="AK97" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL97" t="n">
         <v>0</v>
@@ -13611,7 +13611,7 @@
         <v>2</v>
       </c>
       <c r="AN97" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO97" t="n">
         <v>2</v>
@@ -13620,7 +13620,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.004</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="98">
@@ -13700,10 +13700,10 @@
         <v>886.619</v>
       </c>
       <c r="Z98" t="n">
-        <v>0.00386034932710091</v>
+        <v>0.01297976099655</v>
       </c>
       <c r="AA98" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB98" t="n">
         <v>1.57722843935837</v>
@@ -13712,7 +13712,7 @@
         <v>144</v>
       </c>
       <c r="AD98" t="n">
-        <v>7.90013129831008</v>
+        <v>2.34960154886877</v>
       </c>
       <c r="AE98" t="n">
         <v>1</v>
@@ -13724,7 +13724,7 @@
         <v>44</v>
       </c>
       <c r="AH98" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI98" t="n">
         <v>4.4717060557538</v>
@@ -13733,7 +13733,7 @@
         <v>46</v>
       </c>
       <c r="AK98" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL98" t="n">
         <v>0</v>
@@ -13742,7 +13742,7 @@
         <v>2</v>
       </c>
       <c r="AN98" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO98" t="n">
         <v>2</v>
@@ -13751,7 +13751,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ98" t="n">
-        <v>0.0039</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="99">
@@ -13831,10 +13831,10 @@
         <v>995.924</v>
       </c>
       <c r="Z99" t="n">
-        <v>0.00269217697908576</v>
+        <v>0.00905198229176568</v>
       </c>
       <c r="AA99" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB99" t="n">
         <v>1.57684651632166</v>
@@ -13843,7 +13843,7 @@
         <v>206</v>
       </c>
       <c r="AD99" t="n">
-        <v>7.32068911706348</v>
+        <v>2.17726792615693</v>
       </c>
       <c r="AE99" t="n">
         <v>1</v>
@@ -13855,13 +13855,13 @@
         <v>152</v>
       </c>
       <c r="AH99" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI99" t="n">
         <v>4.0402610959604</v>
       </c>
       <c r="AJ99" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK99" t="s">
         <v>153</v>
@@ -13873,7 +13873,7 @@
         <v>0</v>
       </c>
       <c r="AN99" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO99" t="n">
         <v>2</v>
@@ -13882,7 +13882,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ99" t="n">
-        <v>0.0027</v>
+        <v>0.0091</v>
       </c>
     </row>
     <row r="100">
@@ -13962,10 +13962,10 @@
         <v>292.935</v>
       </c>
       <c r="Z100" t="n">
-        <v>0.00170310903744764</v>
+        <v>0.00572641136436635</v>
       </c>
       <c r="AA100" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB100" t="n">
         <v>1.133784016358</v>
@@ -13974,7 +13974,7 @@
         <v>234</v>
       </c>
       <c r="AD100" t="n">
-        <v>1.10795877226112</v>
+        <v>0.329521314151365</v>
       </c>
       <c r="AE100" t="n">
         <v>1</v>
@@ -13995,7 +13995,7 @@
         <v>46</v>
       </c>
       <c r="AK100" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL100" t="n">
         <v>0</v>
@@ -14004,7 +14004,7 @@
         <v>2</v>
       </c>
       <c r="AN100" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO100" t="n">
         <v>2</v>
@@ -14013,7 +14013,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ100" t="n">
-        <v>0.0017</v>
+        <v>0.0057</v>
       </c>
     </row>
     <row r="101">
@@ -14093,10 +14093,10 @@
         <v>653.898</v>
       </c>
       <c r="Z101" t="n">
-        <v>0.00319380057904216</v>
+        <v>0.0107386054146924</v>
       </c>
       <c r="AA101" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB101" t="n">
         <v>1.90715520291375</v>
@@ -14105,7 +14105,7 @@
         <v>210</v>
       </c>
       <c r="AD101" t="n">
-        <v>2.77598781035714</v>
+        <v>0.825614792028985</v>
       </c>
       <c r="AE101" t="n">
         <v>1</v>
@@ -14117,7 +14117,7 @@
         <v>44</v>
       </c>
       <c r="AH101" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI101" t="n">
         <v>1.98455745379066</v>
@@ -14126,7 +14126,7 @@
         <v>46</v>
       </c>
       <c r="AK101" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL101" t="n">
         <v>0</v>
@@ -14135,7 +14135,7 @@
         <v>2</v>
       </c>
       <c r="AN101" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO101" t="n">
         <v>2</v>
@@ -14144,7 +14144,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ101" t="n">
-        <v>0.0032</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="102">
@@ -14224,10 +14224,10 @@
         <v>664.731</v>
       </c>
       <c r="Z102" t="n">
-        <v>0.00285623480077493</v>
+        <v>0.00960359851473045</v>
       </c>
       <c r="AA102" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB102" t="n">
         <v>1.90143631023016</v>
@@ -14236,7 +14236,7 @@
         <v>234</v>
       </c>
       <c r="AD102" t="n">
-        <v>1.47641095475819</v>
+        <v>0.439103773732052</v>
       </c>
       <c r="AE102" t="n">
         <v>1</v>
@@ -14245,7 +14245,7 @@
         <v>2.38273207017118</v>
       </c>
       <c r="AG102" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH102" t="s">
         <v>45</v>
@@ -14254,10 +14254,10 @@
         <v>0.982555489369581</v>
       </c>
       <c r="AJ102" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK102" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL102" t="n">
         <v>0</v>
@@ -14266,7 +14266,7 @@
         <v>2</v>
       </c>
       <c r="AN102" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO102" t="n">
         <v>2</v>
@@ -14275,7 +14275,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.0029</v>
+        <v>0.0096</v>
       </c>
     </row>
     <row r="103">
@@ -14355,10 +14355,10 @@
         <v>322.178</v>
       </c>
       <c r="Z103" t="n">
-        <v>0.00151100119409303</v>
+        <v>0.00508048176550847</v>
       </c>
       <c r="AA103" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB103" t="n">
         <v>1.38580395229675</v>
@@ -14367,7 +14367,7 @@
         <v>323</v>
       </c>
       <c r="AD103" t="n">
-        <v>0.912339640394968</v>
+        <v>0.271341646261618</v>
       </c>
       <c r="AE103" t="n">
         <v>1</v>
@@ -14388,7 +14388,7 @@
         <v>46</v>
       </c>
       <c r="AK103" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL103" t="n">
         <v>0</v>
@@ -14397,7 +14397,7 @@
         <v>2</v>
       </c>
       <c r="AN103" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO103" t="n">
         <v>2</v>
@@ -14406,7 +14406,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ103" t="n">
-        <v>0.0015</v>
+        <v>0.0051</v>
       </c>
     </row>
     <row r="104">
@@ -14486,10 +14486,10 @@
         <v>1028.79</v>
       </c>
       <c r="Z104" t="n">
-        <v>0.00155573866343376</v>
+        <v>0.00523090381554331</v>
       </c>
       <c r="AA104" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB104" t="n">
         <v>1.89800116938918</v>
@@ -14498,7 +14498,7 @@
         <v>429</v>
       </c>
       <c r="AD104" t="n">
-        <v>3.90226448679913</v>
+        <v>1.16058408855054</v>
       </c>
       <c r="AE104" t="n">
         <v>1</v>
@@ -14519,7 +14519,7 @@
         <v>46</v>
       </c>
       <c r="AK104" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL104" t="n">
         <v>0</v>
@@ -14528,7 +14528,7 @@
         <v>2</v>
       </c>
       <c r="AN104" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO104" t="n">
         <v>2</v>
@@ -14537,7 +14537,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ104" t="n">
-        <v>0.0016</v>
+        <v>0.0052</v>
       </c>
     </row>
     <row r="105">
@@ -14617,10 +14617,10 @@
         <v>1004.53</v>
       </c>
       <c r="Z105" t="n">
-        <v>0.00216103875819981</v>
+        <v>0.0072661213296932</v>
       </c>
       <c r="AA105" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB105" t="n">
         <v>1.89553971076384</v>
@@ -14629,7 +14629,7 @@
         <v>309</v>
       </c>
       <c r="AD105" t="n">
-        <v>4.70509016569595</v>
+        <v>1.39935486176681</v>
       </c>
       <c r="AE105" t="n">
         <v>1</v>
@@ -14650,7 +14650,7 @@
         <v>46</v>
       </c>
       <c r="AK105" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL105" t="n">
         <v>0</v>
@@ -14659,7 +14659,7 @@
         <v>2</v>
       </c>
       <c r="AN105" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO105" t="n">
         <v>2</v>
@@ -14668,7 +14668,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ105" t="n">
-        <v>0.0022</v>
+        <v>0.0073</v>
       </c>
     </row>
     <row r="106">
@@ -14748,10 +14748,10 @@
         <v>1294.77</v>
       </c>
       <c r="Z106" t="n">
-        <v>0.00172279879019107</v>
+        <v>0.006090420573018</v>
       </c>
       <c r="AA106" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB106" t="n">
         <v>1.57513032246041</v>
@@ -14760,7 +14760,7 @@
         <v>321</v>
       </c>
       <c r="AD106" t="n">
-        <v>6.12525136885379</v>
+        <v>1.73265138611739</v>
       </c>
       <c r="AE106" t="n">
         <v>1</v>
@@ -14781,7 +14781,7 @@
         <v>46</v>
       </c>
       <c r="AK106" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL106" t="n">
         <v>0</v>
@@ -14790,7 +14790,7 @@
         <v>2</v>
       </c>
       <c r="AN106" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO106" t="n">
         <v>2</v>
@@ -14799,7 +14799,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0.0017</v>
+        <v>0.0061</v>
       </c>
     </row>
     <row r="107">
@@ -14879,10 +14879,10 @@
         <v>846.492</v>
       </c>
       <c r="Z107" t="n">
-        <v>0.00360245653625698</v>
+        <v>0.0127353673143625</v>
       </c>
       <c r="AA107" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB107" t="n">
         <v>1.57478814299234</v>
@@ -14891,7 +14891,7 @@
         <v>154</v>
       </c>
       <c r="AD107" t="n">
-        <v>5.94159841049766</v>
+        <v>1.68070142787105</v>
       </c>
       <c r="AE107" t="n">
         <v>1</v>
@@ -14912,7 +14912,7 @@
         <v>46</v>
       </c>
       <c r="AK107" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL107" t="n">
         <v>0</v>
@@ -14921,7 +14921,7 @@
         <v>2</v>
       </c>
       <c r="AN107" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO107" t="n">
         <v>2</v>
@@ -14930,7 +14930,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ107" t="n">
-        <v>0.0036</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="108">
@@ -15010,10 +15010,10 @@
         <v>957.131</v>
       </c>
       <c r="Z108" t="n">
-        <v>0.00327862381364406</v>
+        <v>0.0110238089594488</v>
       </c>
       <c r="AA108" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB108" t="n">
         <v>1.57373943054915</v>
@@ -15022,7 +15022,7 @@
         <v>168</v>
       </c>
       <c r="AD108" t="n">
-        <v>5.68405149367972</v>
+        <v>1.69051066230463</v>
       </c>
       <c r="AE108" t="n">
         <v>1</v>
@@ -15031,7 +15031,7 @@
         <v>1.01627147925812</v>
       </c>
       <c r="AG108" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH108" t="s">
         <v>45</v>
@@ -15043,7 +15043,7 @@
         <v>46</v>
       </c>
       <c r="AK108" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AL108" t="n">
         <v>1</v>
@@ -15052,7 +15052,7 @@
         <v>1</v>
       </c>
       <c r="AN108" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO108" t="n">
         <v>2</v>
@@ -15061,7 +15061,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ108" t="n">
-        <v>0.0033</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="109">
@@ -15141,10 +15141,10 @@
         <v>306.909</v>
       </c>
       <c r="Z109" t="n">
-        <v>0.00275958813388409</v>
+        <v>0.00927864071141726</v>
       </c>
       <c r="AA109" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB109" t="n">
         <v>1.6794064929066</v>
@@ -15153,7 +15153,7 @@
         <v>214</v>
       </c>
       <c r="AD109" t="n">
-        <v>1.27313647812085</v>
+        <v>0.378647306982602</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -15162,19 +15162,19 @@
         <v>1.13549714470475</v>
       </c>
       <c r="AG109" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH109" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI109" t="n">
         <v>-0.748339783699342</v>
       </c>
       <c r="AJ109" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK109" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL109" t="n">
         <v>2</v>
@@ -15183,7 +15183,7 @@
         <v>0</v>
       </c>
       <c r="AN109" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO109" t="n">
         <v>2</v>
@@ -15192,7 +15192,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ109" t="n">
-        <v>0.0028</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="110">
@@ -15272,10 +15272,10 @@
         <v>638.918</v>
       </c>
       <c r="Z110" t="n">
-        <v>0.00276742044750641</v>
+        <v>0.00930497551955344</v>
       </c>
       <c r="AA110" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB110" t="n">
         <v>1.88975281986867</v>
@@ -15284,7 +15284,7 @@
         <v>240</v>
       </c>
       <c r="AD110" t="n">
-        <v>2.25867689656129</v>
+        <v>0.67175981438305</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -15305,7 +15305,7 @@
         <v>46</v>
       </c>
       <c r="AK110" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL110" t="n">
         <v>0</v>
@@ -15314,7 +15314,7 @@
         <v>2</v>
       </c>
       <c r="AN110" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO110" t="n">
         <v>2</v>
@@ -15323,7 +15323,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ110" t="n">
-        <v>0.0028</v>
+        <v>0.0093</v>
       </c>
     </row>
     <row r="111">
@@ -15403,10 +15403,10 @@
         <v>650.39</v>
       </c>
       <c r="Z111" t="n">
-        <v>0.00382620018322293</v>
+        <v>0.0128649403706907</v>
       </c>
       <c r="AA111" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB111" t="n">
         <v>1.89123609056448</v>
@@ -15415,7 +15415,7 @@
         <v>174</v>
       </c>
       <c r="AD111" t="n">
-        <v>3.55621363516151</v>
+        <v>1.05766407541493</v>
       </c>
       <c r="AE111" t="n">
         <v>1</v>
@@ -15427,25 +15427,25 @@
         <v>44</v>
       </c>
       <c r="AH111" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI111" t="n">
-        <v>2.35397385040123</v>
+        <v>2.38835636673944</v>
       </c>
       <c r="AJ111" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK111" t="s">
         <v>51</v>
       </c>
-      <c r="AK111" t="s">
-        <v>52</v>
-      </c>
       <c r="AL111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM111" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN111" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO111" t="n">
         <v>2</v>
@@ -15454,7 +15454,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.0038</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="112">
@@ -15534,10 +15534,10 @@
         <v>1642.57</v>
       </c>
       <c r="Z112" t="n">
-        <v>0.00115993019881844</v>
+        <v>0.00410057331498658</v>
       </c>
       <c r="AA112" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB112" t="n">
         <v>1.57419098411074</v>
@@ -15546,7 +15546,7 @@
         <v>477</v>
       </c>
       <c r="AD112" t="n">
-        <v>6.40131433675561</v>
+        <v>1.81074138686789</v>
       </c>
       <c r="AE112" t="n">
         <v>1</v>
@@ -15555,7 +15555,7 @@
         <v>1.01562870791941</v>
       </c>
       <c r="AG112" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH112" t="s">
         <v>45</v>
@@ -15564,10 +15564,10 @@
         <v>3.52691196038282</v>
       </c>
       <c r="AJ112" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK112" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL112" t="n">
         <v>2</v>
@@ -15576,7 +15576,7 @@
         <v>0</v>
       </c>
       <c r="AN112" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO112" t="n">
         <v>2</v>
@@ -15585,7 +15585,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ112" t="n">
-        <v>0.0012</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="113">
@@ -15665,10 +15665,10 @@
         <v>811.615</v>
       </c>
       <c r="Z113" t="n">
-        <v>0.00240627965841124</v>
+        <v>0.00850665511228802</v>
       </c>
       <c r="AA113" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB113" t="n">
         <v>1.57439440507478</v>
@@ -15677,7 +15677,7 @@
         <v>230</v>
       </c>
       <c r="AD113" t="n">
-        <v>4.44134801596451</v>
+        <v>1.25632522368313</v>
       </c>
       <c r="AE113" t="n">
         <v>1</v>
@@ -15686,19 +15686,19 @@
         <v>1.01294193113415</v>
       </c>
       <c r="AG113" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH113" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI113" t="n">
         <v>2.44735171356357</v>
       </c>
       <c r="AJ113" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK113" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL113" t="n">
         <v>2</v>
@@ -15707,7 +15707,7 @@
         <v>0</v>
       </c>
       <c r="AN113" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO113" t="n">
         <v>2</v>
@@ -15716,7 +15716,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ113" t="n">
-        <v>0.0024</v>
+        <v>0.0085</v>
       </c>
     </row>
     <row r="114">
@@ -15796,10 +15796,10 @@
         <v>881.608</v>
       </c>
       <c r="Z114" t="n">
-        <v>0.00304861975626643</v>
+        <v>0.0102504598555115</v>
       </c>
       <c r="AA114" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB114" t="n">
         <v>1.57657193109778</v>
@@ -15808,7 +15808,7 @@
         <v>182</v>
       </c>
       <c r="AD114" t="n">
-        <v>4.97738624358014</v>
+        <v>1.4803392482522</v>
       </c>
       <c r="AE114" t="n">
         <v>1</v>
@@ -15817,7 +15817,7 @@
         <v>1.01572580349547</v>
       </c>
       <c r="AG114" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH114" t="s">
         <v>45</v>
@@ -15826,10 +15826,10 @@
         <v>2.74652260465124</v>
       </c>
       <c r="AJ114" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK114" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL114" t="n">
         <v>2</v>
@@ -15838,7 +15838,7 @@
         <v>0</v>
       </c>
       <c r="AN114" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO114" t="n">
         <v>2</v>
@@ -15847,7 +15847,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ114" t="n">
-        <v>0.003</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="115">
@@ -15927,10 +15927,10 @@
         <v>1032.96</v>
       </c>
       <c r="Z115" t="n">
-        <v>0.00291632548916007</v>
+        <v>0.00980564312449716</v>
       </c>
       <c r="AA115" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB115" t="n">
         <v>1.57481576414644</v>
@@ -15939,7 +15939,7 @@
         <v>190</v>
       </c>
       <c r="AD115" t="n">
-        <v>5.23567194641314</v>
+        <v>1.55715676741886</v>
       </c>
       <c r="AE115" t="n">
         <v>1</v>
@@ -15951,7 +15951,7 @@
         <v>44</v>
       </c>
       <c r="AH115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI115" t="n">
         <v>3.00357260687828</v>
@@ -15960,7 +15960,7 @@
         <v>46</v>
       </c>
       <c r="AK115" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL115" t="n">
         <v>0</v>
@@ -15969,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="AN115" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO115" t="n">
         <v>2</v>
@@ -15978,7 +15978,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ115" t="n">
-        <v>0.0029</v>
+        <v>0.0098</v>
       </c>
     </row>
     <row r="116">
@@ -16058,10 +16058,10 @@
         <v>866.116</v>
       </c>
       <c r="Z116" t="n">
-        <v>0.0037767460617745</v>
+        <v>0.0126986593887628</v>
       </c>
       <c r="AA116" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB116" t="n">
         <v>1.57544264291165</v>
@@ -16070,7 +16070,7 @@
         <v>146</v>
       </c>
       <c r="AD116" t="n">
-        <v>6.66031619638881</v>
+        <v>1.98086445149821</v>
       </c>
       <c r="AE116" t="n">
         <v>1</v>
@@ -16079,7 +16079,7 @@
         <v>1.03592828010014</v>
       </c>
       <c r="AG116" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH116" t="s">
         <v>45</v>
@@ -16091,7 +16091,7 @@
         <v>46</v>
       </c>
       <c r="AK116" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL116" t="n">
         <v>0</v>
@@ -16100,7 +16100,7 @@
         <v>2</v>
       </c>
       <c r="AN116" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO116" t="n">
         <v>2</v>
@@ -16109,7 +16109,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ116" t="n">
-        <v>0.0038</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="117">
@@ -16189,10 +16189,10 @@
         <v>904.496</v>
       </c>
       <c r="Z117" t="n">
-        <v>0.00202660189844595</v>
+        <v>0.00716442219827865</v>
       </c>
       <c r="AA117" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB117" t="n">
         <v>1.57495918964942</v>
@@ -16201,7 +16201,7 @@
         <v>273</v>
       </c>
       <c r="AD117" t="n">
-        <v>4.01211544996771</v>
+        <v>1.13490810042468</v>
       </c>
       <c r="AE117" t="n">
         <v>1</v>
@@ -16213,7 +16213,7 @@
         <v>44</v>
       </c>
       <c r="AH117" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI117" t="n">
         <v>2.25585651114478</v>
@@ -16222,7 +16222,7 @@
         <v>46</v>
       </c>
       <c r="AK117" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL117" t="n">
         <v>0</v>
@@ -16231,7 +16231,7 @@
         <v>2</v>
       </c>
       <c r="AN117" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO117" t="n">
         <v>2</v>
@@ -16240,7 +16240,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ117" t="n">
-        <v>0.002</v>
+        <v>0.0072</v>
       </c>
     </row>
     <row r="118">
@@ -16320,10 +16320,10 @@
         <v>882.611</v>
       </c>
       <c r="Z118" t="n">
-        <v>0.00179807536604004</v>
+        <v>0.00635653755012943</v>
       </c>
       <c r="AA118" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AB118" t="n">
         <v>1.57716896392655</v>
@@ -16332,7 +16332,7 @@
         <v>309</v>
       </c>
       <c r="AD118" t="n">
-        <v>3.64113828246586</v>
+        <v>1.02996969630328</v>
       </c>
       <c r="AE118" t="n">
         <v>1</v>
@@ -16344,7 +16344,7 @@
         <v>44</v>
       </c>
       <c r="AH118" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI118" t="n">
         <v>2.09947635646198</v>
@@ -16353,7 +16353,7 @@
         <v>46</v>
       </c>
       <c r="AK118" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL118" t="n">
         <v>0</v>
@@ -16362,7 +16362,7 @@
         <v>2</v>
       </c>
       <c r="AN118" t="n">
-        <v>0.35</v>
+        <v>1.23731640206218</v>
       </c>
       <c r="AO118" t="n">
         <v>2</v>
@@ -16371,7 +16371,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ118" t="n">
-        <v>0.0018</v>
+        <v>0.0064</v>
       </c>
     </row>
     <row r="119">
@@ -16451,10 +16451,10 @@
         <v>1140.56</v>
       </c>
       <c r="Z119" t="n">
-        <v>0.00218819908323069</v>
+        <v>0.00735744325359642</v>
       </c>
       <c r="AA119" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB119" t="n">
         <v>1.5755033399261</v>
@@ -16463,7 +16463,7 @@
         <v>253</v>
       </c>
       <c r="AD119" t="n">
-        <v>5.6301226786495</v>
+        <v>1.67447153301183</v>
       </c>
       <c r="AE119" t="n">
         <v>1</v>
@@ -16484,7 +16484,7 @@
         <v>46</v>
       </c>
       <c r="AK119" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL119" t="n">
         <v>0</v>
@@ -16493,7 +16493,7 @@
         <v>2</v>
       </c>
       <c r="AN119" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO119" t="n">
         <v>2</v>
@@ -16502,7 +16502,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ119" t="n">
-        <v>0.0022</v>
+        <v>0.0074</v>
       </c>
     </row>
     <row r="120">
@@ -16582,10 +16582,10 @@
         <v>1145.78</v>
       </c>
       <c r="Z120" t="n">
-        <v>0.00324517758838861</v>
+        <v>0.0109113517766221</v>
       </c>
       <c r="AA120" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB120" t="n">
         <v>1.57622911436018</v>
@@ -16594,7 +16594,7 @@
         <v>171</v>
       </c>
       <c r="AD120" t="n">
-        <v>8.87982084513399</v>
+        <v>2.64097393113796</v>
       </c>
       <c r="AE120" t="n">
         <v>1</v>
@@ -16603,7 +16603,7 @@
         <v>1.24943713533511</v>
       </c>
       <c r="AG120" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH120" t="s">
         <v>45</v>
@@ -16615,7 +16615,7 @@
         <v>46</v>
       </c>
       <c r="AK120" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL120" t="n">
         <v>0</v>
@@ -16624,7 +16624,7 @@
         <v>2</v>
       </c>
       <c r="AN120" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO120" t="n">
         <v>2</v>
@@ -16633,7 +16633,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0.0032</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="121">
@@ -16713,10 +16713,10 @@
         <v>710.866</v>
       </c>
       <c r="Z121" t="n">
-        <v>0.00178408943187771</v>
+        <v>0.00599869401965082</v>
       </c>
       <c r="AA121" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB121" t="n">
         <v>1.56999870005239</v>
@@ -16725,7 +16725,7 @@
         <v>310</v>
       </c>
       <c r="AD121" t="n">
-        <v>2.45909417909395</v>
+        <v>0.731366514534924</v>
       </c>
       <c r="AE121" t="n">
         <v>1</v>
@@ -16746,7 +16746,7 @@
         <v>46</v>
       </c>
       <c r="AK121" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL121" t="n">
         <v>0</v>
@@ -16755,7 +16755,7 @@
         <v>2</v>
       </c>
       <c r="AN121" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO121" t="n">
         <v>2</v>
@@ -16764,7 +16764,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0.0018</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="122">
@@ -16844,10 +16844,10 @@
         <v>594.827</v>
       </c>
       <c r="Z122" t="n">
-        <v>0.00490926722266104</v>
+        <v>0.0165065671054674</v>
       </c>
       <c r="AA122" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB122" t="n">
         <v>1.57096551125153</v>
@@ -16856,7 +16856,7 @@
         <v>112</v>
       </c>
       <c r="AD122" t="n">
-        <v>0.826357916522268</v>
+        <v>0.245769566006582</v>
       </c>
       <c r="AE122" t="n">
         <v>1</v>
@@ -16877,7 +16877,7 @@
         <v>46</v>
       </c>
       <c r="AK122" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL122" t="n">
         <v>0</v>
@@ -16886,7 +16886,7 @@
         <v>2</v>
       </c>
       <c r="AN122" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO122" t="n">
         <v>2</v>
@@ -16895,7 +16895,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.0049</v>
+        <v>0.017</v>
       </c>
     </row>
     <row r="123">
@@ -16975,10 +16975,10 @@
         <v>625.082</v>
       </c>
       <c r="Z123" t="n">
-        <v>0.00429773654803209</v>
+        <v>0.0144504003376003</v>
       </c>
       <c r="AA123" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB123" t="n">
         <v>1.57174365185174</v>
@@ -16987,7 +16987,7 @@
         <v>129</v>
       </c>
       <c r="AD123" t="n">
-        <v>1.61798156159388</v>
+        <v>0.481208709021747</v>
       </c>
       <c r="AE123" t="n">
         <v>1</v>
@@ -17008,7 +17008,7 @@
         <v>46</v>
       </c>
       <c r="AK123" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL123" t="n">
         <v>0</v>
@@ -17017,7 +17017,7 @@
         <v>2</v>
       </c>
       <c r="AN123" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO123" t="n">
         <v>2</v>
@@ -17026,7 +17026,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.0043</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="124">
@@ -17106,10 +17106,10 @@
         <v>638.374</v>
       </c>
       <c r="Z124" t="n">
-        <v>0.00610204183594319</v>
+        <v>0.0205170666979437</v>
       </c>
       <c r="AA124" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB124" t="n">
         <v>1.56909647209968</v>
@@ -17118,7 +17118,7 @@
         <v>90</v>
       </c>
       <c r="AD124" t="n">
-        <v>3.16965586580354</v>
+        <v>0.942696779389736</v>
       </c>
       <c r="AE124" t="n">
         <v>1</v>
@@ -17130,7 +17130,7 @@
         <v>44</v>
       </c>
       <c r="AH124" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI124" t="n">
         <v>1.9132355693911</v>
@@ -17139,7 +17139,7 @@
         <v>46</v>
       </c>
       <c r="AK124" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL124" t="n">
         <v>0</v>
@@ -17148,7 +17148,7 @@
         <v>2</v>
       </c>
       <c r="AN124" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO124" t="n">
         <v>2</v>
@@ -17157,7 +17157,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0.0061</v>
+        <v>0.021</v>
       </c>
     </row>
     <row r="125">
@@ -17237,10 +17237,10 @@
         <v>330.913</v>
       </c>
       <c r="Z125" t="n">
-        <v>0.00427661032862707</v>
+        <v>0.0143793670565672</v>
       </c>
       <c r="AA125" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB125" t="n">
         <v>2.8470005902003</v>
@@ -17249,7 +17249,7 @@
         <v>234</v>
       </c>
       <c r="AD125" t="n">
-        <v>0.847486987955283</v>
+        <v>0.25205362599123</v>
       </c>
       <c r="AE125" t="n">
         <v>1</v>
@@ -17258,7 +17258,7 @@
         <v>1.09184054526407</v>
       </c>
       <c r="AG125" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH125" t="s">
         <v>45</v>
@@ -17267,10 +17267,10 @@
         <v>-0.844478584213519</v>
       </c>
       <c r="AJ125" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK125" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="AL125" t="n">
         <v>2</v>
@@ -17279,7 +17279,7 @@
         <v>0</v>
       </c>
       <c r="AN125" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO125" t="n">
         <v>2</v>
@@ -17288,7 +17288,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0.0043</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="126">
@@ -17368,10 +17368,10 @@
         <v>649.238</v>
       </c>
       <c r="Z126" t="n">
-        <v>0.00363593570450617</v>
+        <v>0.0122252087685428</v>
       </c>
       <c r="AA126" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB126" t="n">
         <v>1.88029817861605</v>
@@ -17380,7 +17380,7 @@
         <v>182</v>
       </c>
       <c r="AD126" t="n">
-        <v>2.73371625708397</v>
+        <v>0.813042683630613</v>
       </c>
       <c r="AE126" t="n">
         <v>1</v>
@@ -17389,7 +17389,7 @@
         <v>2.15361882916527</v>
       </c>
       <c r="AG126" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="AH126" t="s">
         <v>45</v>
@@ -17398,10 +17398,10 @@
         <v>1.79907059466682</v>
       </c>
       <c r="AJ126" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK126" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL126" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
         <v>2</v>
       </c>
       <c r="AN126" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO126" t="n">
         <v>2</v>
@@ -17419,7 +17419,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0.0036</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="127">
@@ -17499,10 +17499,10 @@
         <v>431.721</v>
       </c>
       <c r="Z127" t="n">
-        <v>0.00554456360518178</v>
+        <v>0.0186426419806613</v>
       </c>
       <c r="AA127" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB127" t="n">
         <v>2.28119188327479</v>
@@ -17511,7 +17511,7 @@
         <v>145</v>
       </c>
       <c r="AD127" t="n">
-        <v>0.346381433540522</v>
+        <v>0.103018332482687</v>
       </c>
       <c r="AE127" t="n">
         <v>1</v>
@@ -17523,25 +17523,25 @@
         <v>44</v>
       </c>
       <c r="AH127" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI127" t="n">
-        <v>0.276556880148404</v>
+        <v>0.278340430612751</v>
       </c>
       <c r="AJ127" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK127" t="s">
         <v>51</v>
       </c>
-      <c r="AK127" t="s">
-        <v>52</v>
-      </c>
       <c r="AL127" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN127" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO127" t="n">
         <v>2</v>
@@ -17550,7 +17550,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ127" t="n">
-        <v>0.0055</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="128">
@@ -17630,10 +17630,10 @@
         <v>633.83</v>
       </c>
       <c r="Z128" t="n">
-        <v>0.00253555010639317</v>
+        <v>0.00852535135737986</v>
       </c>
       <c r="AA128" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB128" t="n">
         <v>1.57204106596377</v>
@@ -17642,7 +17642,7 @@
         <v>218</v>
       </c>
       <c r="AD128" t="n">
-        <v>2.29607137728374</v>
+        <v>0.682881418126952</v>
       </c>
       <c r="AE128" t="n">
         <v>1</v>
@@ -17663,7 +17663,7 @@
         <v>46</v>
       </c>
       <c r="AK128" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL128" t="n">
         <v>0</v>
@@ -17672,7 +17672,7 @@
         <v>2</v>
       </c>
       <c r="AN128" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO128" t="n">
         <v>2</v>
@@ -17681,7 +17681,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ128" t="n">
-        <v>0.0025</v>
+        <v>0.0085</v>
       </c>
     </row>
     <row r="129">
@@ -17761,10 +17761,10 @@
         <v>689.099</v>
       </c>
       <c r="Z129" t="n">
-        <v>0.00294069034051501</v>
+        <v>0.00988756574872276</v>
       </c>
       <c r="AA129" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB129" t="n">
         <v>1.57116883907516</v>
@@ -17773,7 +17773,7 @@
         <v>188</v>
       </c>
       <c r="AD129" t="n">
-        <v>2.01625120818721</v>
+        <v>0.599659269293227</v>
       </c>
       <c r="AE129" t="n">
         <v>1</v>
@@ -17794,7 +17794,7 @@
         <v>46</v>
       </c>
       <c r="AK129" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL129" t="n">
         <v>0</v>
@@ -17803,7 +17803,7 @@
         <v>2</v>
       </c>
       <c r="AN129" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO129" t="n">
         <v>2</v>
@@ -17812,7 +17812,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ129" t="n">
-        <v>0.0029</v>
+        <v>0.0099</v>
       </c>
     </row>
     <row r="130">
@@ -17892,10 +17892,10 @@
         <v>623.597</v>
       </c>
       <c r="Z130" t="n">
-        <v>0.00323290639304831</v>
+        <v>0.0108700919917781</v>
       </c>
       <c r="AA130" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB130" t="n">
         <v>1.57026881948061</v>
@@ -17904,7 +17904,7 @@
         <v>171</v>
       </c>
       <c r="AD130" t="n">
-        <v>3.04705083628809</v>
+        <v>0.90623245286516</v>
       </c>
       <c r="AE130" t="n">
         <v>1</v>
@@ -17916,7 +17916,7 @@
         <v>44</v>
       </c>
       <c r="AH130" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI130" t="n">
         <v>1.79256446324334</v>
@@ -17925,7 +17925,7 @@
         <v>46</v>
       </c>
       <c r="AK130" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL130" t="n">
         <v>0</v>
@@ -17934,7 +17934,7 @@
         <v>2</v>
       </c>
       <c r="AN130" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO130" t="n">
         <v>2</v>
@@ -17943,7 +17943,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.0032</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="131">
@@ -18023,10 +18023,10 @@
         <v>786.519</v>
       </c>
       <c r="Z131" t="n">
-        <v>0.00123054309218426</v>
+        <v>0.00413748961017013</v>
       </c>
       <c r="AA131" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB131" t="n">
         <v>1.56806348318338</v>
@@ -18035,7 +18035,7 @@
         <v>448</v>
       </c>
       <c r="AD131" t="n">
-        <v>2.07498146847966</v>
+        <v>0.617126410703665</v>
       </c>
       <c r="AE131" t="n">
         <v>1</v>
@@ -18044,7 +18044,7 @@
         <v>1.30533963049728</v>
       </c>
       <c r="AG131" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AH131" t="s">
         <v>45</v>
@@ -18056,7 +18056,7 @@
         <v>46</v>
       </c>
       <c r="AK131" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL131" t="n">
         <v>0</v>
@@ -18065,7 +18065,7 @@
         <v>2</v>
       </c>
       <c r="AN131" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO131" t="n">
         <v>2</v>
@@ -18074,7 +18074,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ131" t="n">
-        <v>0.0012</v>
+        <v>0.0041</v>
       </c>
     </row>
     <row r="132">
@@ -18154,10 +18154,10 @@
         <v>399.032</v>
       </c>
       <c r="Z132" t="n">
-        <v>0.00574765248463385</v>
+        <v>0.0193254934256948</v>
       </c>
       <c r="AA132" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB132" t="n">
         <v>3.1365760701859</v>
@@ -18166,7 +18166,7 @@
         <v>192</v>
       </c>
       <c r="AD132" t="n">
-        <v>0.0453660792570742</v>
+        <v>0.0134924605761079</v>
       </c>
       <c r="AE132" t="n">
         <v>1</v>
@@ -18178,7 +18178,7 @@
         <v>44</v>
       </c>
       <c r="AH132" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI132" t="n">
         <v>-0.0499493452718085</v>
@@ -18187,7 +18187,7 @@
         <v>46</v>
       </c>
       <c r="AK132" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="AL132" t="n">
         <v>1</v>
@@ -18196,7 +18196,7 @@
         <v>1</v>
       </c>
       <c r="AN132" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO132" t="n">
         <v>2</v>
@@ -18205,7 +18205,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ132" t="n">
-        <v>0.0057</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="133">
@@ -18285,10 +18285,10 @@
         <v>610.971</v>
       </c>
       <c r="Z133" t="n">
-        <v>0.00243797229010416</v>
+        <v>0.00819726272428515</v>
       </c>
       <c r="AA133" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB133" t="n">
         <v>1.57423353589583</v>
@@ -18297,7 +18297,7 @@
         <v>227</v>
       </c>
       <c r="AD133" t="n">
-        <v>2.08459114579647</v>
+        <v>0.619984453419049</v>
       </c>
       <c r="AE133" t="n">
         <v>1</v>
@@ -18318,7 +18318,7 @@
         <v>46</v>
       </c>
       <c r="AK133" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL133" t="n">
         <v>0</v>
@@ -18327,7 +18327,7 @@
         <v>2</v>
       </c>
       <c r="AN133" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO133" t="n">
         <v>2</v>
@@ -18336,7 +18336,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ133" t="n">
-        <v>0.0024</v>
+        <v>0.0082</v>
       </c>
     </row>
     <row r="134">
@@ -18416,10 +18416,10 @@
         <v>654.442</v>
       </c>
       <c r="Z134" t="n">
-        <v>0.00233420103929979</v>
+        <v>0.00784834973231889</v>
       </c>
       <c r="AA134" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB134" t="n">
         <v>1.57391841507072</v>
@@ -18428,7 +18428,7 @@
         <v>237</v>
       </c>
       <c r="AD134" t="n">
-        <v>2.39577722554708</v>
+        <v>0.712535231040282</v>
       </c>
       <c r="AE134" t="n">
         <v>1</v>
@@ -18440,7 +18440,7 @@
         <v>44</v>
       </c>
       <c r="AH134" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI134" t="n">
         <v>1.39489834156636</v>
@@ -18449,7 +18449,7 @@
         <v>46</v>
       </c>
       <c r="AK134" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL134" t="n">
         <v>0</v>
@@ -18458,7 +18458,7 @@
         <v>2</v>
       </c>
       <c r="AN134" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO134" t="n">
         <v>2</v>
@@ -18467,7 +18467,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ134" t="n">
-        <v>0.0023</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="135">
@@ -18547,10 +18547,10 @@
         <v>456.126</v>
       </c>
       <c r="Z135" t="n">
-        <v>0.00447246215963583</v>
+        <v>0.0150378851702996</v>
       </c>
       <c r="AA135" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB135" t="n">
         <v>1.87843410704705</v>
@@ -18559,7 +18559,7 @@
         <v>148</v>
       </c>
       <c r="AD135" t="n">
-        <v>0.798293863199134</v>
+        <v>0.237422952429454</v>
       </c>
       <c r="AE135" t="n">
         <v>1</v>
@@ -18568,7 +18568,7 @@
         <v>2.94774623101831</v>
       </c>
       <c r="AG135" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AH135" t="s">
         <v>45</v>
@@ -18577,10 +18577,10 @@
         <v>0.524839847027861</v>
       </c>
       <c r="AJ135" t="s">
-        <v>51</v>
+        <v>76</v>
       </c>
       <c r="AK135" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AL135" t="n">
         <v>0</v>
@@ -18589,7 +18589,7 @@
         <v>2</v>
       </c>
       <c r="AN135" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO135" t="n">
         <v>2</v>
@@ -18598,7 +18598,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ135" t="n">
-        <v>0.0045</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="136">
@@ -18678,10 +18678,10 @@
         <v>631.86</v>
       </c>
       <c r="Z136" t="n">
-        <v>0.00231421192777099</v>
+        <v>0.00778113978104431</v>
       </c>
       <c r="AA136" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB136" t="n">
         <v>1.56705207680493</v>
@@ -18690,7 +18690,7 @@
         <v>239</v>
       </c>
       <c r="AD136" t="n">
-        <v>2.24928303175245</v>
+        <v>0.66896595710761</v>
       </c>
       <c r="AE136" t="n">
         <v>1</v>
@@ -18702,7 +18702,7 @@
         <v>44</v>
       </c>
       <c r="AH136" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AI136" t="n">
         <v>1.27424702626894</v>
@@ -18711,7 +18711,7 @@
         <v>46</v>
       </c>
       <c r="AK136" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL136" t="n">
         <v>0</v>
@@ -18720,7 +18720,7 @@
         <v>2</v>
       </c>
       <c r="AN136" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO136" t="n">
         <v>2</v>
@@ -18729,7 +18729,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ136" t="n">
-        <v>0.0023</v>
+        <v>0.0078</v>
       </c>
     </row>
     <row r="137">
@@ -18809,10 +18809,10 @@
         <v>727.058</v>
       </c>
       <c r="Z137" t="n">
-        <v>0.00197684334562831</v>
+        <v>0.00664679591915206</v>
       </c>
       <c r="AA137" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AB137" t="n">
         <v>1.57017842881335</v>
@@ -18821,7 +18821,7 @@
         <v>280</v>
       </c>
       <c r="AD137" t="n">
-        <v>2.97455080130357</v>
+        <v>0.884670001804492</v>
       </c>
       <c r="AE137" t="n">
         <v>1</v>
@@ -18842,7 +18842,7 @@
         <v>46</v>
       </c>
       <c r="AK137" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AL137" t="n">
         <v>0</v>
@@ -18851,7 +18851,7 @@
         <v>2</v>
       </c>
       <c r="AN137" t="n">
-        <v>0.35</v>
+        <v>1.17681483302553</v>
       </c>
       <c r="AO137" t="n">
         <v>2</v>
@@ -18860,7 +18860,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ137" t="n">
-        <v>0.002</v>
+        <v>0.0066</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/results/CO2_best_all.xlsx
+++ b/data processing/goFlux_reprocessing/results/CO2_best_all.xlsx
@@ -1445,7 +1445,7 @@
         <v>50</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.263527302392572</v>
+        <v>-0.394589604545401</v>
       </c>
       <c r="C5" t="n">
         <v>364.107056689531</v>
@@ -1466,10 +1466,10 @@
         <v>739.38900337117</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000695245376310336</v>
+        <v>0.00104101719541467</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.263822901839082</v>
+        <v>-0.263822762541858</v>
       </c>
       <c r="K5" t="n">
         <v>0.998269885766586</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.300098826663761</v>
+        <v>-0.449349559847087</v>
       </c>
       <c r="N5" t="n">
         <v>365.954503352097</v>
@@ -1499,10 +1499,10 @@
         <v>899.100064927906</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00417574448152551</v>
+        <v>0.00625250013455046</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.39145645051259</v>
+        <v>-1.39145571583027</v>
       </c>
       <c r="V5" t="n">
         <v>0.996751357702747</v>
@@ -1517,13 +1517,13 @@
         <v>277.555</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.00746531810001655</v>
+        <v>0.0111781090237965</v>
       </c>
       <c r="AA5" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.749948527791428</v>
+        <v>1.12292688584425</v>
       </c>
       <c r="AC5" t="n">
         <v>250</v>
@@ -1544,7 +1544,7 @@
         <v>44</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.300098826663761</v>
+        <v>-0.449349559847087</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
@@ -1568,7 +1568,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.0075</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="6">
@@ -1576,7 +1576,7 @@
         <v>52</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.658380583624297</v>
+        <v>-0.844818870177976</v>
       </c>
       <c r="C6" t="n">
         <v>446.571638299557</v>
@@ -1597,10 +1597,10 @@
         <v>691.544971966273</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00176620177857339</v>
+        <v>0.00226634996362695</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.268264560423499</v>
+        <v>-0.268264600097001</v>
       </c>
       <c r="K6" t="n">
         <v>0.998713457661317</v>
@@ -1609,7 +1609,7 @@
         <v>1.98883532059287e-259</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.806475562382559</v>
+        <v>-1.03485095153866</v>
       </c>
       <c r="N6" t="n">
         <v>451.945035269018</v>
@@ -1630,10 +1630,10 @@
         <v>862.474862167953</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0131369034106168</v>
+        <v>0.0168569757589479</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.62892764807487</v>
+        <v>-1.62892788897611</v>
       </c>
       <c r="V6" t="n">
         <v>0.996719612677832</v>
@@ -1648,13 +1648,13 @@
         <v>293.745</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.0103154801498813</v>
+        <v>0.0132365876247334</v>
       </c>
       <c r="AA6" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.747952360000791</v>
+        <v>0.959755320007132</v>
       </c>
       <c r="AC6" t="n">
         <v>180</v>
@@ -1675,7 +1675,7 @@
         <v>44</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.806475562382559</v>
+        <v>-1.03485095153866</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
@@ -1699,7 +1699,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="7">
@@ -1969,7 +1969,7 @@
         <v>55</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.490131414829546</v>
+        <v>-0.733892691182196</v>
       </c>
       <c r="C9" t="n">
         <v>383.195451920007</v>
@@ -1990,10 +1990,10 @@
         <v>1136.31389110451</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00278111652795029</v>
+        <v>0.00416427315944879</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.567422622546543</v>
+        <v>-0.567422623154993</v>
       </c>
       <c r="K9" t="n">
         <v>0.993156805527823</v>
@@ -2002,7 +2002,7 @@
         <v>9.48729968710112e-233</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.62327024692296</v>
+        <v>-0.933246604907294</v>
       </c>
       <c r="N9" t="n">
         <v>389.178282128386</v>
@@ -2023,10 +2023,10 @@
         <v>932.561221351942</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0082595640900911</v>
+        <v>0.0123673642234844</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.32519787858765</v>
+        <v>-1.32519788000867</v>
       </c>
       <c r="V9" t="n">
         <v>0.997372826389476</v>
@@ -2041,13 +2041,13 @@
         <v>254.221</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.00864097368457913</v>
+        <v>0.012938463522106</v>
       </c>
       <c r="AA9" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.749045008064568</v>
+        <v>1.12157401087272</v>
       </c>
       <c r="AC9" t="n">
         <v>215</v>
@@ -2068,7 +2068,7 @@
         <v>45</v>
       </c>
       <c r="AI9" t="n">
-        <v>-0.62327024692296</v>
+        <v>-0.933246604907294</v>
       </c>
       <c r="AJ9" t="s">
         <v>46</v>
@@ -2092,7 +2092,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.0086</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="10">
@@ -2100,7 +2100,7 @@
         <v>56</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.395758448378302</v>
+        <v>-0.592584404816105</v>
       </c>
       <c r="C10" t="n">
         <v>388.740113479359</v>
@@ -2121,10 +2121,10 @@
         <v>815.974693326938</v>
       </c>
       <c r="I10" t="n">
-        <v>0.00145583881382619</v>
+        <v>0.00217988380582831</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.367860451189804</v>
+        <v>-0.367860474914925</v>
       </c>
       <c r="K10" t="n">
         <v>0.997193179176985</v>
@@ -2133,7 +2133,7 @@
         <v>2.61594103238256e-266</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.461160692941333</v>
+        <v>-0.69051371075217</v>
       </c>
       <c r="N10" t="n">
         <v>391.388214996008</v>
@@ -2154,10 +2154,10 @@
         <v>1012.4230181394</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0104307241552974</v>
+        <v>0.0156183270106916</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.26184154784942</v>
+        <v>-2.26184169372665</v>
       </c>
       <c r="V10" t="n">
         <v>0.992897400268458</v>
@@ -2172,13 +2172,13 @@
         <v>277.161</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.008946942935693</v>
+        <v>0.0133966030951368</v>
       </c>
       <c r="AA10" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.75019898291531</v>
+        <v>1.1233019019712</v>
       </c>
       <c r="AC10" t="n">
         <v>209</v>
@@ -2199,7 +2199,7 @@
         <v>44</v>
       </c>
       <c r="AI10" t="n">
-        <v>-0.461160692941333</v>
+        <v>-0.69051371075217</v>
       </c>
       <c r="AJ10" t="s">
         <v>46</v>
@@ -2223,7 +2223,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0089</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="11">
@@ -2231,7 +2231,7 @@
         <v>57</v>
       </c>
       <c r="B11" t="n">
-        <v>0.340678943816397</v>
+        <v>0.510111736040167</v>
       </c>
       <c r="C11" t="n">
         <v>255.469420118019</v>
@@ -2252,10 +2252,10 @@
         <v>763.743358325277</v>
       </c>
       <c r="I11" t="n">
-        <v>0.00215312844539309</v>
+        <v>0.00322396058227074</v>
       </c>
       <c r="J11" t="n">
-        <v>0.632011013440703</v>
+        <v>0.632010666387978</v>
       </c>
       <c r="K11" t="n">
         <v>0.992900540593155</v>
@@ -2264,7 +2264,7 @@
         <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000209002651912593</v>
       </c>
       <c r="M11" t="n">
-        <v>0.346085541661996</v>
+        <v>0.518207243740743</v>
       </c>
       <c r="N11" t="n">
         <v>255.254069577292</v>
@@ -2285,10 +2285,10 @@
         <v>766.300180216227</v>
       </c>
       <c r="T11" t="n">
-        <v>0.00868303838523345</v>
+        <v>0.0130014414830848</v>
       </c>
       <c r="U11" t="n">
-        <v>2.50892838329367</v>
+        <v>2.5089270055803</v>
       </c>
       <c r="V11" t="n">
         <v>0.992882381548797</v>
@@ -2303,13 +2303,13 @@
         <v>335.969</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0102884971242673</v>
+        <v>0.0154053639785051</v>
       </c>
       <c r="AA11" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.74599588125286</v>
+        <v>1.11700843557211</v>
       </c>
       <c r="AC11" t="n">
         <v>180</v>
@@ -2330,7 +2330,7 @@
         <v>44</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.346085541661996</v>
+        <v>0.518207243740743</v>
       </c>
       <c r="AJ11" t="s">
         <v>46</v>
@@ -2354,7 +2354,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
     </row>
     <row r="12">
@@ -2624,7 +2624,7 @@
         <v>60</v>
       </c>
       <c r="B14" t="n">
-        <v>-0.236992797939244</v>
+        <v>-0.354858466541911</v>
       </c>
       <c r="C14" t="n">
         <v>401.22778840176</v>
@@ -2645,10 +2645,10 @@
         <v>719.727757946015</v>
       </c>
       <c r="I14" t="n">
-        <v>0.00129195601292755</v>
+        <v>0.00193449485140984</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.545145685506765</v>
+        <v>-0.545145468913694</v>
       </c>
       <c r="K14" t="n">
         <v>0.994061905107379</v>
@@ -2657,7 +2657,7 @@
         <v>7.94810184353364e-225</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.257758382004878</v>
+        <v>-0.385951577313434</v>
       </c>
       <c r="N14" t="n">
         <v>402.113829622541</v>
@@ -2678,10 +2678,10 @@
         <v>735.476276766027</v>
       </c>
       <c r="T14" t="n">
-        <v>0.00568257737669342</v>
+        <v>0.00850873912730337</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.20461400032604</v>
+        <v>-2.20461312440585</v>
       </c>
       <c r="V14" t="n">
         <v>0.993646470084973</v>
@@ -2696,13 +2696,13 @@
         <v>339.96</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.00918624180755692</v>
+        <v>0.0137549145352026</v>
       </c>
       <c r="AA14" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.747937638288551</v>
+        <v>1.11991590335203</v>
       </c>
       <c r="AC14" t="n">
         <v>202</v>
@@ -2723,7 +2723,7 @@
         <v>44</v>
       </c>
       <c r="AI14" t="n">
-        <v>-0.257758382004878</v>
+        <v>-0.385951577313434</v>
       </c>
       <c r="AJ14" t="s">
         <v>46</v>
@@ -2747,7 +2747,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.0092</v>
+        <v>0.014</v>
       </c>
     </row>
     <row r="15">
@@ -2886,7 +2886,7 @@
         <v>62</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.313144471260615</v>
+        <v>-0.5869238600472</v>
       </c>
       <c r="C16" t="n">
         <v>374.303827518841</v>
@@ -2907,10 +2907,10 @@
         <v>1094.11086673799</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00100052065739725</v>
+        <v>0.00187526586402535</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.319507687097106</v>
+        <v>-0.319507519062957</v>
       </c>
       <c r="K16" t="n">
         <v>0.997210641650461</v>
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.371713531323036</v>
+        <v>-0.696699321427015</v>
       </c>
       <c r="N16" t="n">
         <v>377.542839284047</v>
@@ -2940,10 +2940,10 @@
         <v>1286.83835027965</v>
       </c>
       <c r="T16" t="n">
-        <v>0.00644692604688561</v>
+        <v>0.0120834090273264</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.73438024274746</v>
+        <v>-1.73437933060944</v>
       </c>
       <c r="V16" t="n">
         <v>0.994427943333383</v>
@@ -2958,13 +2958,13 @@
         <v>263.572</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.00672567766618544</v>
+        <v>0.0126058770297928</v>
       </c>
       <c r="AA16" t="n">
         <v>2.46870127774823</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.746479818010103</v>
+        <v>1.39912039471771</v>
       </c>
       <c r="AC16" t="n">
         <v>275</v>
@@ -2985,7 +2985,7 @@
         <v>44</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.371713531323036</v>
+        <v>-0.696699321427015</v>
       </c>
       <c r="AJ16" t="s">
         <v>46</v>
@@ -3009,7 +3009,7 @@
         <v>0.5</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.0067</v>
+        <v>0.013</v>
       </c>
     </row>
     <row r="17">
